--- a/Report JSS 1G.xlsx
+++ b/Report JSS 1G.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PythonSetup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771"/>
   </bookViews>
@@ -19,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Report!$A$2:$N$57</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -2165,23 +2170,43 @@
     <xf numFmtId="0" fontId="32" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2198,72 +2223,23 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2292,6 +2268,64 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2301,40 +2335,11 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="32">
     <cellStyle name="Hyperlink" xfId="31" builtinId="8"/>
@@ -3298,7 +3303,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3389,7 +3394,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3485,7 +3490,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9476,14 +9481,14 @@
     </row>
     <row r="2" spans="1:216">
       <c r="A2" s="126"/>
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="256" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="233"/>
+      <c r="C2" s="256"/>
+      <c r="D2" s="256"/>
+      <c r="E2" s="256"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="256"/>
       <c r="H2" s="127"/>
       <c r="I2" s="127"/>
       <c r="J2" s="128"/>
@@ -9492,28 +9497,28 @@
       <c r="M2" s="126"/>
       <c r="N2" s="129"/>
       <c r="O2" s="113"/>
-      <c r="P2" s="237" t="s">
+      <c r="P2" s="259" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="260"/>
+      <c r="S2" s="260"/>
+      <c r="T2" s="260"/>
+      <c r="U2" s="260"/>
+      <c r="V2" s="260"/>
       <c r="W2" s="130"/>
       <c r="X2" s="130"/>
       <c r="Y2" s="131"/>
       <c r="Z2" s="132"/>
-      <c r="AA2" s="234" t="s">
+      <c r="AA2" s="250" t="s">
         <v>98</v>
       </c>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="234"/>
-      <c r="AD2" s="234"/>
-      <c r="AE2" s="234"/>
-      <c r="AF2" s="234"/>
-      <c r="AG2" s="234"/>
+      <c r="AB2" s="250"/>
+      <c r="AC2" s="250"/>
+      <c r="AD2" s="250"/>
+      <c r="AE2" s="250"/>
+      <c r="AF2" s="250"/>
+      <c r="AG2" s="250"/>
       <c r="AH2" s="132"/>
       <c r="AI2" s="132"/>
       <c r="AJ2" s="132"/>
@@ -9533,197 +9538,197 @@
       <c r="AV2" s="133"/>
       <c r="AW2" s="111"/>
       <c r="AX2" s="45"/>
-      <c r="AY2" s="235" t="s">
+      <c r="AY2" s="257" t="s">
         <v>93</v>
       </c>
-      <c r="AZ2" s="235"/>
-      <c r="BA2" s="235"/>
-      <c r="BB2" s="235"/>
-      <c r="BC2" s="235"/>
-      <c r="BD2" s="235"/>
-      <c r="BE2" s="235"/>
+      <c r="AZ2" s="257"/>
+      <c r="BA2" s="257"/>
+      <c r="BB2" s="257"/>
+      <c r="BC2" s="257"/>
+      <c r="BD2" s="257"/>
+      <c r="BE2" s="257"/>
       <c r="BF2" s="45"/>
       <c r="BG2" s="45"/>
       <c r="BH2" s="45"/>
       <c r="BI2" s="111"/>
       <c r="BJ2" s="135"/>
-      <c r="BK2" s="236" t="s">
+      <c r="BK2" s="258" t="s">
         <v>64</v>
       </c>
-      <c r="BL2" s="236"/>
-      <c r="BM2" s="236"/>
-      <c r="BN2" s="236"/>
-      <c r="BO2" s="236"/>
-      <c r="BP2" s="236"/>
-      <c r="BQ2" s="236"/>
+      <c r="BL2" s="258"/>
+      <c r="BM2" s="258"/>
+      <c r="BN2" s="258"/>
+      <c r="BO2" s="258"/>
+      <c r="BP2" s="258"/>
+      <c r="BQ2" s="258"/>
       <c r="BR2" s="135"/>
       <c r="BS2" s="135"/>
       <c r="BT2" s="135"/>
       <c r="BU2" s="111"/>
       <c r="BV2" s="136"/>
-      <c r="BW2" s="239" t="s">
+      <c r="BW2" s="251" t="s">
         <v>87</v>
       </c>
-      <c r="BX2" s="239"/>
-      <c r="BY2" s="239"/>
-      <c r="BZ2" s="239"/>
-      <c r="CA2" s="239"/>
-      <c r="CB2" s="239"/>
-      <c r="CC2" s="239"/>
+      <c r="BX2" s="251"/>
+      <c r="BY2" s="251"/>
+      <c r="BZ2" s="251"/>
+      <c r="CA2" s="251"/>
+      <c r="CB2" s="251"/>
+      <c r="CC2" s="251"/>
       <c r="CD2" s="136"/>
       <c r="CE2" s="136"/>
       <c r="CF2" s="136"/>
       <c r="CG2" s="111"/>
       <c r="CH2" s="137"/>
-      <c r="CI2" s="240" t="s">
+      <c r="CI2" s="252" t="s">
         <v>88</v>
       </c>
-      <c r="CJ2" s="240"/>
-      <c r="CK2" s="240"/>
-      <c r="CL2" s="240"/>
-      <c r="CM2" s="240"/>
-      <c r="CN2" s="240"/>
-      <c r="CO2" s="240"/>
+      <c r="CJ2" s="252"/>
+      <c r="CK2" s="252"/>
+      <c r="CL2" s="252"/>
+      <c r="CM2" s="252"/>
+      <c r="CN2" s="252"/>
+      <c r="CO2" s="252"/>
       <c r="CP2" s="137"/>
       <c r="CQ2" s="137"/>
       <c r="CR2" s="137"/>
       <c r="CS2" s="111"/>
       <c r="CT2" s="138"/>
-      <c r="CU2" s="241" t="s">
+      <c r="CU2" s="253" t="s">
         <v>67</v>
       </c>
-      <c r="CV2" s="241"/>
-      <c r="CW2" s="241"/>
-      <c r="CX2" s="241"/>
-      <c r="CY2" s="241"/>
-      <c r="CZ2" s="241"/>
-      <c r="DA2" s="241"/>
+      <c r="CV2" s="253"/>
+      <c r="CW2" s="253"/>
+      <c r="CX2" s="253"/>
+      <c r="CY2" s="253"/>
+      <c r="CZ2" s="253"/>
+      <c r="DA2" s="253"/>
       <c r="DB2" s="138"/>
       <c r="DC2" s="138"/>
       <c r="DD2" s="138"/>
       <c r="DE2" s="111"/>
       <c r="DF2" s="129"/>
-      <c r="DG2" s="242" t="s">
+      <c r="DG2" s="254" t="s">
         <v>89</v>
       </c>
-      <c r="DH2" s="242"/>
-      <c r="DI2" s="242"/>
-      <c r="DJ2" s="242"/>
-      <c r="DK2" s="242"/>
-      <c r="DL2" s="242"/>
-      <c r="DM2" s="242"/>
+      <c r="DH2" s="254"/>
+      <c r="DI2" s="254"/>
+      <c r="DJ2" s="254"/>
+      <c r="DK2" s="254"/>
+      <c r="DL2" s="254"/>
+      <c r="DM2" s="254"/>
       <c r="DN2" s="129"/>
       <c r="DO2" s="129"/>
       <c r="DP2" s="129"/>
       <c r="DQ2" s="111"/>
       <c r="DR2" s="139"/>
-      <c r="DS2" s="243" t="s">
+      <c r="DS2" s="255" t="s">
         <v>90</v>
       </c>
-      <c r="DT2" s="243"/>
-      <c r="DU2" s="243"/>
-      <c r="DV2" s="243"/>
-      <c r="DW2" s="243"/>
-      <c r="DX2" s="243"/>
-      <c r="DY2" s="243"/>
+      <c r="DT2" s="255"/>
+      <c r="DU2" s="255"/>
+      <c r="DV2" s="255"/>
+      <c r="DW2" s="255"/>
+      <c r="DX2" s="255"/>
+      <c r="DY2" s="255"/>
       <c r="DZ2" s="139"/>
       <c r="EA2" s="139"/>
       <c r="EB2" s="139"/>
       <c r="EC2" s="111"/>
       <c r="ED2" s="140"/>
-      <c r="EE2" s="246" t="s">
+      <c r="EE2" s="247" t="s">
         <v>65</v>
       </c>
-      <c r="EF2" s="246"/>
-      <c r="EG2" s="246"/>
-      <c r="EH2" s="246"/>
-      <c r="EI2" s="246"/>
-      <c r="EJ2" s="246"/>
-      <c r="EK2" s="246"/>
+      <c r="EF2" s="247"/>
+      <c r="EG2" s="247"/>
+      <c r="EH2" s="247"/>
+      <c r="EI2" s="247"/>
+      <c r="EJ2" s="247"/>
+      <c r="EK2" s="247"/>
       <c r="EL2" s="140"/>
       <c r="EM2" s="140"/>
       <c r="EN2" s="140"/>
       <c r="EO2" s="111"/>
       <c r="EP2" s="141"/>
-      <c r="EQ2" s="247" t="s">
+      <c r="EQ2" s="248" t="s">
         <v>68</v>
       </c>
-      <c r="ER2" s="247"/>
-      <c r="ES2" s="247"/>
-      <c r="ET2" s="247"/>
-      <c r="EU2" s="247"/>
-      <c r="EV2" s="247"/>
-      <c r="EW2" s="247"/>
+      <c r="ER2" s="248"/>
+      <c r="ES2" s="248"/>
+      <c r="ET2" s="248"/>
+      <c r="EU2" s="248"/>
+      <c r="EV2" s="248"/>
+      <c r="EW2" s="248"/>
       <c r="EX2" s="141"/>
       <c r="EY2" s="141"/>
       <c r="EZ2" s="141"/>
       <c r="FA2" s="111"/>
       <c r="FB2" s="142"/>
-      <c r="FC2" s="245" t="s">
+      <c r="FC2" s="246" t="s">
         <v>66</v>
       </c>
-      <c r="FD2" s="245"/>
-      <c r="FE2" s="245"/>
-      <c r="FF2" s="245"/>
-      <c r="FG2" s="245"/>
-      <c r="FH2" s="245"/>
-      <c r="FI2" s="245"/>
+      <c r="FD2" s="246"/>
+      <c r="FE2" s="246"/>
+      <c r="FF2" s="246"/>
+      <c r="FG2" s="246"/>
+      <c r="FH2" s="246"/>
+      <c r="FI2" s="246"/>
       <c r="FJ2" s="142"/>
       <c r="FK2" s="142"/>
       <c r="FL2" s="142"/>
       <c r="FM2" s="111"/>
       <c r="FN2" s="128"/>
-      <c r="FO2" s="248" t="s">
+      <c r="FO2" s="249" t="s">
         <v>94</v>
       </c>
-      <c r="FP2" s="248"/>
-      <c r="FQ2" s="248"/>
-      <c r="FR2" s="248"/>
-      <c r="FS2" s="248"/>
-      <c r="FT2" s="248"/>
-      <c r="FU2" s="248"/>
+      <c r="FP2" s="249"/>
+      <c r="FQ2" s="249"/>
+      <c r="FR2" s="249"/>
+      <c r="FS2" s="249"/>
+      <c r="FT2" s="249"/>
+      <c r="FU2" s="249"/>
       <c r="FV2" s="128"/>
       <c r="FW2" s="128"/>
       <c r="FX2" s="128"/>
       <c r="FY2" s="111"/>
       <c r="FZ2" s="132"/>
-      <c r="GA2" s="234" t="s">
+      <c r="GA2" s="250" t="s">
         <v>95</v>
       </c>
-      <c r="GB2" s="234"/>
-      <c r="GC2" s="234"/>
-      <c r="GD2" s="234"/>
-      <c r="GE2" s="234"/>
-      <c r="GF2" s="234"/>
-      <c r="GG2" s="234"/>
+      <c r="GB2" s="250"/>
+      <c r="GC2" s="250"/>
+      <c r="GD2" s="250"/>
+      <c r="GE2" s="250"/>
+      <c r="GF2" s="250"/>
+      <c r="GG2" s="250"/>
       <c r="GH2" s="132"/>
       <c r="GI2" s="132"/>
       <c r="GJ2" s="132"/>
       <c r="GK2" s="111"/>
       <c r="GL2" s="142"/>
-      <c r="GM2" s="245" t="s">
+      <c r="GM2" s="246" t="s">
         <v>63</v>
       </c>
-      <c r="GN2" s="245"/>
-      <c r="GO2" s="245"/>
-      <c r="GP2" s="245"/>
-      <c r="GQ2" s="245"/>
-      <c r="GR2" s="245"/>
-      <c r="GS2" s="245"/>
+      <c r="GN2" s="246"/>
+      <c r="GO2" s="246"/>
+      <c r="GP2" s="246"/>
+      <c r="GQ2" s="246"/>
+      <c r="GR2" s="246"/>
+      <c r="GS2" s="246"/>
       <c r="GT2" s="142"/>
       <c r="GU2" s="142"/>
       <c r="GV2" s="142"/>
       <c r="GW2" s="111"/>
       <c r="GX2" s="143"/>
-      <c r="GY2" s="244" t="s">
+      <c r="GY2" s="245" t="s">
         <v>83</v>
       </c>
-      <c r="GZ2" s="244"/>
-      <c r="HA2" s="244"/>
-      <c r="HB2" s="244"/>
-      <c r="HC2" s="244"/>
-      <c r="HD2" s="244"/>
-      <c r="HE2" s="244"/>
+      <c r="GZ2" s="245"/>
+      <c r="HA2" s="245"/>
+      <c r="HB2" s="245"/>
+      <c r="HC2" s="245"/>
+      <c r="HD2" s="245"/>
+      <c r="HE2" s="245"/>
       <c r="HF2" s="143"/>
       <c r="HG2" s="143"/>
       <c r="HH2" s="143"/>
@@ -43638,6 +43643,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="AY2:BE2"/>
+    <mergeCell ref="BK2:BQ2"/>
+    <mergeCell ref="P2:V2"/>
+    <mergeCell ref="BW2:CC2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CU2:DA2"/>
+    <mergeCell ref="DG2:DM2"/>
+    <mergeCell ref="DS2:DY2"/>
     <mergeCell ref="GY2:HE2"/>
     <mergeCell ref="GM2:GS2"/>
     <mergeCell ref="EE2:EK2"/>
@@ -43645,16 +43660,6 @@
     <mergeCell ref="FC2:FI2"/>
     <mergeCell ref="FO2:FU2"/>
     <mergeCell ref="GA2:GG2"/>
-    <mergeCell ref="BW2:CC2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CU2:DA2"/>
-    <mergeCell ref="DG2:DM2"/>
-    <mergeCell ref="DS2:DY2"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="AA2:AG2"/>
-    <mergeCell ref="AY2:BE2"/>
-    <mergeCell ref="BK2:BQ2"/>
-    <mergeCell ref="P2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43816,114 +43821,114 @@
       <c r="A10" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="249" t="e">
+      <c r="B10" s="299" t="e">
         <f>VLOOKUP(B14,Data!#REF!,2,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
+      <c r="C10" s="299"/>
+      <c r="D10" s="299"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="299"/>
+      <c r="G10" s="299"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
-      <c r="K10" s="250" t="s">
+      <c r="K10" s="300" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="250"/>
-      <c r="M10" s="251" t="e">
+      <c r="L10" s="300"/>
+      <c r="M10" s="295" t="e">
         <f>VLOOKUP(B14,Data!#REF!,7,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="N10" s="252"/>
+      <c r="N10" s="296"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="253" t="e">
+      <c r="B11" s="293" t="e">
         <f>VLOOKUP(B14,Data!#REF!,4,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="253"/>
-      <c r="D11" s="253"/>
-      <c r="E11" s="253"/>
-      <c r="F11" s="253"/>
-      <c r="G11" s="253"/>
+      <c r="C11" s="293"/>
+      <c r="D11" s="293"/>
+      <c r="E11" s="293"/>
+      <c r="F11" s="293"/>
+      <c r="G11" s="293"/>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
-      <c r="K11" s="250" t="s">
+      <c r="K11" s="300" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="250"/>
-      <c r="M11" s="249" t="e">
+      <c r="L11" s="300"/>
+      <c r="M11" s="299" t="e">
         <f>VLOOKUP(B14,Data!#REF!,3,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="N11" s="254"/>
+      <c r="N11" s="301"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="249" t="e">
+      <c r="B12" s="299" t="e">
         <f>VLOOKUP(B14,Data!#REF!,5,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="249"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="249"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="249"/>
+      <c r="C12" s="299"/>
+      <c r="D12" s="299"/>
+      <c r="E12" s="299"/>
+      <c r="F12" s="299"/>
+      <c r="G12" s="299"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="250" t="s">
+      <c r="K12" s="300" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="250"/>
-      <c r="M12" s="249" t="e">
+      <c r="L12" s="300"/>
+      <c r="M12" s="299" t="e">
         <f>VLOOKUP(B14,Data!#REF!,8,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="N12" s="254"/>
+      <c r="N12" s="301"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="249" t="e">
+      <c r="B13" s="299" t="e">
         <f>VLOOKUP(B14,Data!#REF!,6,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="249"/>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
+      <c r="C13" s="299"/>
+      <c r="D13" s="299"/>
+      <c r="E13" s="299"/>
+      <c r="F13" s="299"/>
+      <c r="G13" s="299"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
-      <c r="K13" s="250" t="s">
+      <c r="K13" s="300" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="250"/>
-      <c r="M13" s="249" t="str">
+      <c r="L13" s="300"/>
+      <c r="M13" s="299" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="254"/>
+      <c r="N13" s="301"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="253">
-        <v>31</v>
-      </c>
-      <c r="C14" s="253"/>
+      <c r="B14" s="293">
+        <v>30</v>
+      </c>
+      <c r="C14" s="293"/>
       <c r="D14" s="64"/>
       <c r="E14" s="64"/>
       <c r="F14" s="64"/>
@@ -43931,10 +43936,10 @@
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
-      <c r="K14" s="255"/>
-      <c r="L14" s="255"/>
-      <c r="M14" s="251"/>
-      <c r="N14" s="252"/>
+      <c r="K14" s="294"/>
+      <c r="L14" s="294"/>
+      <c r="M14" s="295"/>
+      <c r="N14" s="296"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="63" t="s">
@@ -43952,10 +43957,10 @@
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
-      <c r="K15" s="256"/>
-      <c r="L15" s="256"/>
-      <c r="M15" s="255"/>
-      <c r="N15" s="257"/>
+      <c r="K15" s="297"/>
+      <c r="L15" s="297"/>
+      <c r="M15" s="294"/>
+      <c r="N15" s="298"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="63" t="s">
@@ -43995,111 +44000,111 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="281" t="s">
+      <c r="A18" s="264" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="283" t="s">
+      <c r="B18" s="266" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="283" t="s">
+      <c r="C18" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="283" t="s">
+      <c r="D18" s="266" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="283" t="s">
+      <c r="E18" s="266" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="285" t="s">
+      <c r="F18" s="268" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="283" t="s">
+      <c r="G18" s="266" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="283" t="s">
+      <c r="H18" s="266" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="285" t="s">
+      <c r="I18" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="287" t="s">
+      <c r="J18" s="270" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="258" t="s">
+      <c r="K18" s="285" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="259"/>
-      <c r="M18" s="260">
+      <c r="L18" s="286"/>
+      <c r="M18" s="287">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="261"/>
+      <c r="N18" s="288"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="282"/>
-      <c r="B19" s="284"/>
-      <c r="C19" s="284"/>
-      <c r="D19" s="284"/>
-      <c r="E19" s="284"/>
-      <c r="F19" s="286"/>
-      <c r="G19" s="284"/>
-      <c r="H19" s="284"/>
-      <c r="I19" s="286"/>
-      <c r="J19" s="288"/>
-      <c r="K19" s="262" t="s">
+      <c r="A19" s="265"/>
+      <c r="B19" s="267"/>
+      <c r="C19" s="267"/>
+      <c r="D19" s="267"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="269"/>
+      <c r="G19" s="267"/>
+      <c r="H19" s="267"/>
+      <c r="I19" s="269"/>
+      <c r="J19" s="271"/>
+      <c r="K19" s="289" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="263"/>
-      <c r="M19" s="264">
+      <c r="L19" s="290"/>
+      <c r="M19" s="277">
         <f>SUM(H23:H40)</f>
-        <v>1277</v>
-      </c>
-      <c r="N19" s="265"/>
+        <v>1422</v>
+      </c>
+      <c r="N19" s="278"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="282"/>
-      <c r="B20" s="284"/>
-      <c r="C20" s="284"/>
-      <c r="D20" s="284"/>
-      <c r="E20" s="284"/>
-      <c r="F20" s="286"/>
-      <c r="G20" s="284"/>
-      <c r="H20" s="284"/>
-      <c r="I20" s="286"/>
-      <c r="J20" s="288"/>
-      <c r="K20" s="262" t="s">
+      <c r="A20" s="265"/>
+      <c r="B20" s="267"/>
+      <c r="C20" s="267"/>
+      <c r="D20" s="267"/>
+      <c r="E20" s="267"/>
+      <c r="F20" s="269"/>
+      <c r="G20" s="267"/>
+      <c r="H20" s="267"/>
+      <c r="I20" s="269"/>
+      <c r="J20" s="271"/>
+      <c r="K20" s="289" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="263"/>
-      <c r="M20" s="266">
+      <c r="L20" s="290"/>
+      <c r="M20" s="291">
         <f>VLOOKUP(B14,Bsheet!A2:V51,21,0)</f>
-        <v>76.764705882352942</v>
-      </c>
-      <c r="N20" s="267"/>
+        <v>85.294117647058826</v>
+      </c>
+      <c r="N20" s="292"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="282"/>
-      <c r="B21" s="284"/>
-      <c r="C21" s="284"/>
-      <c r="D21" s="284"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="286"/>
-      <c r="G21" s="284"/>
-      <c r="H21" s="284"/>
-      <c r="I21" s="286"/>
-      <c r="J21" s="289"/>
-      <c r="K21" s="268" t="s">
+      <c r="A21" s="265"/>
+      <c r="B21" s="267"/>
+      <c r="C21" s="267"/>
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="269"/>
+      <c r="G21" s="267"/>
+      <c r="H21" s="267"/>
+      <c r="I21" s="269"/>
+      <c r="J21" s="272"/>
+      <c r="K21" s="279" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="269"/>
-      <c r="M21" s="270">
+      <c r="L21" s="280"/>
+      <c r="M21" s="281">
         <f>VLOOKUP(B14,Bsheet!A2:V51,22,0)</f>
-        <v>7</v>
-      </c>
-      <c r="N21" s="271"/>
+        <v>2</v>
+      </c>
+      <c r="N21" s="282"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="282"/>
+      <c r="A22" s="265"/>
       <c r="B22" s="28" t="s">
         <v>58</v>
       </c>
@@ -44123,12 +44128,12 @@
       </c>
       <c r="I22" s="58"/>
       <c r="J22" s="59"/>
-      <c r="K22" s="272" t="s">
+      <c r="K22" s="283" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="272"/>
-      <c r="M22" s="272"/>
-      <c r="N22" s="273"/>
+      <c r="L22" s="283"/>
+      <c r="M22" s="283"/>
+      <c r="N22" s="284"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="29" t="s">
@@ -44136,11 +44141,11 @@
       </c>
       <c r="B23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:V53,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:L53,4,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:L53,5,0)</f>
@@ -44152,31 +44157,31 @@
       </c>
       <c r="F23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:L53,7,0)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:L53,8,0)</f>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:K53,9,0)</f>
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I23" s="27">
         <f>VLOOKUP(B14,Scoresheet!A4:K53,10,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!A4:K53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K23" s="274" t="str">
+      <c r="K23" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!A4:L53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L23" s="264"/>
-      <c r="M23" s="264"/>
-      <c r="N23" s="265"/>
+      <c r="L23" s="277"/>
+      <c r="M23" s="277"/>
+      <c r="N23" s="278"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="29" t="s">
@@ -44184,11 +44189,11 @@
       </c>
       <c r="B24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,3,0)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,4,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,5,0)</f>
@@ -44200,31 +44205,31 @@
       </c>
       <c r="F24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,7,0)</f>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,8,0)</f>
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,9,0)</f>
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="I24" s="27">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,10,0)</f>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J24" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!M4:W53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K24" s="274" t="str">
+        <v>A</v>
+      </c>
+      <c r="K24" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!M4:X53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L24" s="264"/>
-      <c r="M24" s="264"/>
-      <c r="N24" s="265"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L24" s="277"/>
+      <c r="M24" s="277"/>
+      <c r="N24" s="278"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="29" t="s">
@@ -44232,7 +44237,7 @@
       </c>
       <c r="B25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,4,0)</f>
@@ -44240,7 +44245,7 @@
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,5,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,6,0)</f>
@@ -44248,31 +44253,31 @@
       </c>
       <c r="F25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,7,0)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,8,0)</f>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,9,0)</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I25" s="27">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,10,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J25" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K25" s="274" t="str">
+      <c r="K25" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y4:AJ53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L25" s="264"/>
-      <c r="M25" s="264"/>
-      <c r="N25" s="265"/>
+      <c r="L25" s="277"/>
+      <c r="M25" s="277"/>
+      <c r="N25" s="278"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="29" t="s">
@@ -44280,7 +44285,7 @@
       </c>
       <c r="B26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,4,0)</f>
@@ -44296,31 +44301,31 @@
       </c>
       <c r="F26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,7,0)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,8,0)</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,9,0)</f>
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,10,0)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J26" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="274" t="str">
+      <c r="K26" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK4:AV53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L26" s="264"/>
-      <c r="M26" s="264"/>
-      <c r="N26" s="265"/>
+      <c r="L26" s="277"/>
+      <c r="M26" s="277"/>
+      <c r="N26" s="278"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="29" t="s">
@@ -44328,7 +44333,7 @@
       </c>
       <c r="B27" s="27">
         <f>VLOOKUP(Report!B14,Scoresheet!AW4:BG53,3,0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C27" s="27">
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,4,0)</f>
@@ -44344,7 +44349,7 @@
       </c>
       <c r="F27" s="27">
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,7,0)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G27" s="27">
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,8,0)</f>
@@ -44352,23 +44357,23 @@
       </c>
       <c r="H27" s="27">
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,9,0)</f>
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I27" s="27">
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,10,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K27" s="274" t="str">
+      <c r="K27" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW4:BH53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L27" s="264"/>
-      <c r="M27" s="264"/>
-      <c r="N27" s="265"/>
+      <c r="L27" s="277"/>
+      <c r="M27" s="277"/>
+      <c r="N27" s="278"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="29" t="s">
@@ -44376,11 +44381,11 @@
       </c>
       <c r="B28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,3,0)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,4,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,5,0)</f>
@@ -44392,31 +44397,31 @@
       </c>
       <c r="F28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,7,0)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,8,0)</f>
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,9,0)</f>
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I28" s="27">
         <f>VLOOKUP(B14,Scoresheet!BI4:BS53,10,0)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J28" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI4:BU53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K28" s="274" t="str">
+        <v>A</v>
+      </c>
+      <c r="K28" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI4:BT53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L28" s="264"/>
-      <c r="M28" s="264"/>
-      <c r="N28" s="265"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L28" s="277"/>
+      <c r="M28" s="277"/>
+      <c r="N28" s="278"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="29" t="s">
@@ -44424,7 +44429,7 @@
       </c>
       <c r="B29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,3,0)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,4,0)</f>
@@ -44432,39 +44437,39 @@
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,5,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,6,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,7,0)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,8,0)</f>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,9,0)</f>
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I29" s="27">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,10,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J29" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K29" s="274" t="str">
+      <c r="K29" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU4:CF53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L29" s="264"/>
-      <c r="M29" s="264"/>
-      <c r="N29" s="265"/>
+      <c r="L29" s="277"/>
+      <c r="M29" s="277"/>
+      <c r="N29" s="278"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="29" t="s">
@@ -44472,15 +44477,15 @@
       </c>
       <c r="B30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,4,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,5,0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,6,0)</f>
@@ -44488,31 +44493,31 @@
       </c>
       <c r="F30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,7,0)</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,8,0)</f>
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,9,0)</f>
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="I30" s="27">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,10,0)</f>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J30" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K30" s="274" t="str">
+        <v>A</v>
+      </c>
+      <c r="K30" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG4:CR53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L30" s="264"/>
-      <c r="M30" s="264"/>
-      <c r="N30" s="265"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L30" s="277"/>
+      <c r="M30" s="277"/>
+      <c r="N30" s="278"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="29" t="s">
@@ -44528,7 +44533,7 @@
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,5,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" s="27">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,6,0)</f>
@@ -44536,31 +44541,31 @@
       </c>
       <c r="F31" s="27">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,7,0)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G31" s="27">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,8,0)</f>
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H31" s="27">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,9,0)</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I31" s="27">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,10,0)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J31" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K31" s="274" t="str">
+      <c r="K31" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS4:DD53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L31" s="264"/>
-      <c r="M31" s="264"/>
-      <c r="N31" s="265"/>
+      <c r="L31" s="277"/>
+      <c r="M31" s="277"/>
+      <c r="N31" s="278"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="29" t="s">
@@ -44576,7 +44581,7 @@
       </c>
       <c r="D32" s="27">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,5,0)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32" s="27">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,6,0)</f>
@@ -44584,31 +44589,31 @@
       </c>
       <c r="F32" s="27">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,7,0)</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G32" s="27">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,8,0)</f>
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H32" s="27">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,9,0)</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I32" s="27">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,10,0)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J32" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K32" s="274" t="str">
+      <c r="K32" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE4:DP53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L32" s="264"/>
-      <c r="M32" s="264"/>
-      <c r="N32" s="265"/>
+      <c r="L32" s="277"/>
+      <c r="M32" s="277"/>
+      <c r="N32" s="278"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="29" t="s">
@@ -44624,39 +44629,39 @@
       </c>
       <c r="D33" s="27">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,5,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" s="27">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,6,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F33" s="27">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,7,0)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G33" s="27">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,8,0)</f>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H33" s="27">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,9,0)</f>
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I33" s="27">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,10,0)</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J33" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K33" s="274" t="str">
+      <c r="K33" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EB53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L33" s="264"/>
-      <c r="M33" s="264"/>
-      <c r="N33" s="265"/>
+      <c r="L33" s="277"/>
+      <c r="M33" s="277"/>
+      <c r="N33" s="278"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
@@ -44664,7 +44669,7 @@
       </c>
       <c r="B34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,3,0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,4,0)</f>
@@ -44676,35 +44681,35 @@
       </c>
       <c r="E34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,6,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,7,0)</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,8,0)</f>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,9,0)</f>
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="I34" s="27">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,10,0)</f>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J34" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K34" s="274" t="str">
+        <v>A</v>
+      </c>
+      <c r="K34" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC4:EN53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L34" s="264"/>
-      <c r="M34" s="264"/>
-      <c r="N34" s="265"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L34" s="277"/>
+      <c r="M34" s="277"/>
+      <c r="N34" s="278"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="29" t="s">
@@ -44712,11 +44717,11 @@
       </c>
       <c r="B35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,4,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,5,0)</f>
@@ -44728,31 +44733,31 @@
       </c>
       <c r="F35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,7,0)</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:FA53,8,0)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,9,0)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,10,0)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J35" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,11,0)</f>
-        <v>P</v>
-      </c>
-      <c r="K35" s="274" t="str">
+        <v>C</v>
+      </c>
+      <c r="K35" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO4:EZ53,12,0)</f>
-        <v>Pass</v>
-      </c>
-      <c r="L35" s="264"/>
-      <c r="M35" s="264"/>
-      <c r="N35" s="265"/>
+        <v>Credit</v>
+      </c>
+      <c r="L35" s="277"/>
+      <c r="M35" s="277"/>
+      <c r="N35" s="278"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="29" t="s">
@@ -44764,7 +44769,7 @@
       </c>
       <c r="C36" s="27">
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,4,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="27">
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,5,0)</f>
@@ -44776,31 +44781,31 @@
       </c>
       <c r="F36" s="27">
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,7,0)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G36" s="27">
         <f>VLOOKUP(B14,Scoresheet!FA4:FL53,8,0)</f>
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="H36" s="27">
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,9,0)</f>
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I36" s="27">
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,10,0)</f>
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J36" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K36" s="274" t="str">
+        <v>A</v>
+      </c>
+      <c r="K36" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA4:FL53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L36" s="264"/>
-      <c r="M36" s="264"/>
-      <c r="N36" s="265"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L36" s="277"/>
+      <c r="M36" s="277"/>
+      <c r="N36" s="278"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="29" t="s">
@@ -44808,11 +44813,11 @@
       </c>
       <c r="B37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,3,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,4,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,5,0)</f>
@@ -44824,31 +44829,31 @@
       </c>
       <c r="F37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,7,0)</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,8,0)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,9,0)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,10,0)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J37" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,11,0)</f>
-        <v>P</v>
-      </c>
-      <c r="K37" s="274" t="str">
+        <v>C</v>
+      </c>
+      <c r="K37" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM4:FX53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L37" s="264"/>
-      <c r="M37" s="264"/>
-      <c r="N37" s="265"/>
+      <c r="L37" s="277"/>
+      <c r="M37" s="277"/>
+      <c r="N37" s="278"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="29" t="s">
@@ -44876,27 +44881,27 @@
       </c>
       <c r="G38" s="27">
         <f>VLOOKUP(B14,Scoresheet!FY4:GI53,8,0)</f>
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H38" s="27">
         <f>VLOOKUP(B14,Scoresheet!FY4:GI53,9,0)</f>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I38" s="27">
         <f>VLOOKUP(B14,Scoresheet!FY4:GI53,10,0)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J38" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY4:GI53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K38" s="274" t="str">
+      <c r="K38" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY4:GJ53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L38" s="264"/>
-      <c r="M38" s="264"/>
-      <c r="N38" s="265"/>
+      <c r="L38" s="277"/>
+      <c r="M38" s="277"/>
+      <c r="N38" s="278"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="29" t="s">
@@ -44908,7 +44913,7 @@
       </c>
       <c r="C39" s="27">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,4,0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" s="27">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,5,0)</f>
@@ -44920,31 +44925,31 @@
       </c>
       <c r="F39" s="27">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,7,0)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G39" s="27">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,8,0)</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H39" s="27">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,9,0)</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I39" s="27">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,10,0)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J39" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K39" s="274" t="str">
+        <v>A</v>
+      </c>
+      <c r="K39" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK4:GW53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L39" s="264"/>
-      <c r="M39" s="264"/>
-      <c r="N39" s="265"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L39" s="277"/>
+      <c r="M39" s="277"/>
+      <c r="N39" s="278"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="29" t="s">
@@ -44986,13 +44991,13 @@
         <f>VLOOKUP(B14,Scoresheet!GW4:HH53,11,0)</f>
         <v/>
       </c>
-      <c r="K40" s="274" t="str">
+      <c r="K40" s="276" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW4:HH53,12,0)</f>
         <v/>
       </c>
-      <c r="L40" s="264"/>
-      <c r="M40" s="264"/>
-      <c r="N40" s="265"/>
+      <c r="L40" s="277"/>
+      <c r="M40" s="277"/>
+      <c r="N40" s="278"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="22"/>
@@ -45016,20 +45021,20 @@
       </c>
       <c r="B42" s="35"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="275" t="s">
+      <c r="D42" s="274" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="275"/>
+      <c r="E42" s="274"/>
       <c r="F42" s="37"/>
       <c r="G42" s="38"/>
-      <c r="H42" s="276" t="s">
+      <c r="H42" s="275" t="s">
         <v>72</v>
       </c>
-      <c r="I42" s="276"/>
-      <c r="J42" s="276"/>
-      <c r="K42" s="276"/>
-      <c r="L42" s="276"/>
-      <c r="M42" s="276"/>
+      <c r="I42" s="275"/>
+      <c r="J42" s="275"/>
+      <c r="K42" s="275"/>
+      <c r="L42" s="275"/>
+      <c r="M42" s="275"/>
       <c r="N42" s="39"/>
       <c r="O42" s="17"/>
     </row>
@@ -45042,23 +45047,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="275" t="s">
+      <c r="D43" s="274" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="275"/>
+      <c r="E43" s="274"/>
       <c r="F43" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>3</v>
       </c>
       <c r="G43" s="38"/>
-      <c r="H43" s="276" t="s">
+      <c r="H43" s="275" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="276"/>
-      <c r="J43" s="276"/>
-      <c r="K43" s="276"/>
-      <c r="L43" s="276"/>
-      <c r="M43" s="276"/>
+      <c r="I43" s="275"/>
+      <c r="J43" s="275"/>
+      <c r="K43" s="275"/>
+      <c r="L43" s="275"/>
+      <c r="M43" s="275"/>
       <c r="N43" s="39"/>
       <c r="O43" s="17"/>
     </row>
@@ -45071,23 +45076,23 @@
         <v>3</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="275" t="s">
+      <c r="D44" s="274" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="275"/>
+      <c r="E44" s="274"/>
       <c r="F44" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>3</v>
       </c>
       <c r="G44" s="38"/>
-      <c r="H44" s="276" t="s">
+      <c r="H44" s="275" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="276"/>
-      <c r="J44" s="276"/>
-      <c r="K44" s="276"/>
-      <c r="L44" s="276"/>
-      <c r="M44" s="276"/>
+      <c r="I44" s="275"/>
+      <c r="J44" s="275"/>
+      <c r="K44" s="275"/>
+      <c r="L44" s="275"/>
+      <c r="M44" s="275"/>
       <c r="N44" s="39"/>
       <c r="O44" s="17"/>
     </row>
@@ -45100,23 +45105,23 @@
         <v>3</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="275" t="s">
+      <c r="D45" s="274" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="275"/>
+      <c r="E45" s="274"/>
       <c r="F45" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>5</v>
       </c>
       <c r="G45" s="38"/>
-      <c r="H45" s="276" t="s">
+      <c r="H45" s="275" t="s">
         <v>75</v>
       </c>
-      <c r="I45" s="276"/>
-      <c r="J45" s="276"/>
-      <c r="K45" s="276"/>
-      <c r="L45" s="276"/>
-      <c r="M45" s="276"/>
+      <c r="I45" s="275"/>
+      <c r="J45" s="275"/>
+      <c r="K45" s="275"/>
+      <c r="L45" s="275"/>
+      <c r="M45" s="275"/>
       <c r="N45" s="39"/>
       <c r="O45" s="17"/>
     </row>
@@ -45129,23 +45134,23 @@
         <v>2</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="275" t="s">
+      <c r="D46" s="274" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="275"/>
+      <c r="E46" s="274"/>
       <c r="F46" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>3</v>
       </c>
       <c r="G46" s="38"/>
-      <c r="H46" s="276" t="s">
+      <c r="H46" s="275" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="276"/>
-      <c r="J46" s="276"/>
-      <c r="K46" s="276"/>
-      <c r="L46" s="276"/>
-      <c r="M46" s="276"/>
+      <c r="I46" s="275"/>
+      <c r="J46" s="275"/>
+      <c r="K46" s="275"/>
+      <c r="L46" s="275"/>
+      <c r="M46" s="275"/>
       <c r="N46" s="39"/>
       <c r="O46" s="17"/>
     </row>
@@ -45158,23 +45163,23 @@
         <v>4</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="275" t="s">
+      <c r="D47" s="274" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="275"/>
+      <c r="E47" s="274"/>
       <c r="F47" s="37">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="38"/>
-      <c r="H47" s="276" t="s">
+      <c r="H47" s="275" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="276"/>
-      <c r="J47" s="276"/>
-      <c r="K47" s="276"/>
-      <c r="L47" s="276"/>
-      <c r="M47" s="276"/>
+      <c r="I47" s="275"/>
+      <c r="J47" s="275"/>
+      <c r="K47" s="275"/>
+      <c r="L47" s="275"/>
+      <c r="M47" s="275"/>
       <c r="N47" s="39"/>
       <c r="O47" s="17"/>
     </row>
@@ -45279,11 +45284,11 @@
       <c r="O52" s="17"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="277" t="s">
+      <c r="A53" s="261" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="278"/>
-      <c r="C53" s="278"/>
+      <c r="B53" s="262"/>
+      <c r="C53" s="262"/>
       <c r="D53" s="17" t="s">
         <v>79</v>
       </c>
@@ -45301,16 +45306,16 @@
       <c r="M53" s="17"/>
       <c r="N53" s="15"/>
       <c r="O53" s="17"/>
-      <c r="R53" s="280"/>
-      <c r="S53" s="280"/>
-      <c r="T53" s="280"/>
+      <c r="R53" s="263"/>
+      <c r="S53" s="263"/>
+      <c r="T53" s="263"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="277" t="s">
+      <c r="A54" s="261" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="278"/>
-      <c r="C54" s="278"/>
+      <c r="B54" s="262"/>
+      <c r="C54" s="262"/>
       <c r="D54" s="17" t="s">
         <v>79</v>
       </c>
@@ -45325,43 +45330,43 @@
       <c r="M54" s="17"/>
       <c r="N54" s="15"/>
       <c r="O54" s="17"/>
-      <c r="R54" s="280"/>
-      <c r="S54" s="280"/>
-      <c r="T54" s="280"/>
+      <c r="R54" s="263"/>
+      <c r="S54" s="263"/>
+      <c r="T54" s="263"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="277" t="s">
+      <c r="A55" s="261" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="278"/>
-      <c r="C55" s="278"/>
+      <c r="B55" s="262"/>
+      <c r="C55" s="262"/>
       <c r="D55" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="279" t="str">
+      <c r="E55" s="273" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="279"/>
-      <c r="G55" s="279"/>
-      <c r="H55" s="279"/>
-      <c r="I55" s="279"/>
-      <c r="J55" s="279"/>
+      <c r="F55" s="273"/>
+      <c r="G55" s="273"/>
+      <c r="H55" s="273"/>
+      <c r="I55" s="273"/>
+      <c r="J55" s="273"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" s="15"/>
       <c r="O55" s="17"/>
-      <c r="R55" s="280"/>
-      <c r="S55" s="280"/>
-      <c r="T55" s="280"/>
+      <c r="R55" s="263"/>
+      <c r="S55" s="263"/>
+      <c r="T55" s="263"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="277" t="s">
+      <c r="A56" s="261" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="278"/>
-      <c r="C56" s="278"/>
+      <c r="B56" s="262"/>
+      <c r="C56" s="262"/>
       <c r="D56" s="17" t="s">
         <v>79</v>
       </c>
@@ -45379,9 +45384,9 @@
       <c r="M56" s="17"/>
       <c r="N56" s="15"/>
       <c r="O56" s="17"/>
-      <c r="R56" s="280"/>
-      <c r="S56" s="280"/>
-      <c r="T56" s="280"/>
+      <c r="R56" s="263"/>
+      <c r="S56" s="263"/>
+      <c r="T56" s="263"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="24"/>
@@ -45418,6 +45423,65 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -45434,65 +45498,6 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -45517,7 +45522,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -45527,1528 +45532,1528 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A1" s="290" t="s">
+      <c r="A1" s="305" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="291"/>
-      <c r="C1" s="291"/>
-      <c r="D1" s="291"/>
-      <c r="E1" s="291"/>
-      <c r="F1" s="291"/>
-      <c r="G1" s="291"/>
-      <c r="H1" s="291"/>
-      <c r="I1" s="291"/>
-      <c r="J1" s="291"/>
-      <c r="K1" s="292"/>
+      <c r="B1" s="306"/>
+      <c r="C1" s="306"/>
+      <c r="D1" s="306"/>
+      <c r="E1" s="306"/>
+      <c r="F1" s="306"/>
+      <c r="G1" s="306"/>
+      <c r="H1" s="306"/>
+      <c r="I1" s="306"/>
+      <c r="J1" s="306"/>
+      <c r="K1" s="307"/>
     </row>
     <row r="2" spans="1:11" s="71" customFormat="1">
-      <c r="A2" s="293" t="s">
+      <c r="A2" s="233" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="294"/>
-      <c r="C2" s="295"/>
-      <c r="D2" s="295"/>
-      <c r="E2" s="295"/>
-      <c r="F2" s="295"/>
-      <c r="G2" s="295"/>
-      <c r="H2" s="295"/>
-      <c r="I2" s="295"/>
-      <c r="J2" s="295"/>
-      <c r="K2" s="296"/>
+      <c r="B2" s="308"/>
+      <c r="C2" s="309"/>
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="309"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="310"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="293" t="s">
+      <c r="A3" s="233" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="297" t="s">
+      <c r="B3" s="311" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="297"/>
-      <c r="D3" s="297"/>
-      <c r="E3" s="297"/>
-      <c r="F3" s="297"/>
-      <c r="G3" s="297"/>
-      <c r="H3" s="297"/>
-      <c r="I3" s="297"/>
-      <c r="J3" s="297"/>
-      <c r="K3" s="298"/>
+      <c r="C3" s="311"/>
+      <c r="D3" s="311"/>
+      <c r="E3" s="311"/>
+      <c r="F3" s="311"/>
+      <c r="G3" s="311"/>
+      <c r="H3" s="311"/>
+      <c r="I3" s="311"/>
+      <c r="J3" s="311"/>
+      <c r="K3" s="312"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="299" t="s">
+      <c r="A4" s="302" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="300"/>
-      <c r="C4" s="300"/>
-      <c r="D4" s="300"/>
-      <c r="E4" s="300"/>
-      <c r="F4" s="300"/>
-      <c r="G4" s="300"/>
-      <c r="H4" s="300"/>
-      <c r="I4" s="300"/>
-      <c r="J4" s="300"/>
-      <c r="K4" s="301"/>
-    </row>
-    <row r="5" spans="1:11" ht="106.5">
-      <c r="A5" s="302" t="s">
+      <c r="B4" s="303"/>
+      <c r="C4" s="303"/>
+      <c r="D4" s="303"/>
+      <c r="E4" s="303"/>
+      <c r="F4" s="303"/>
+      <c r="G4" s="303"/>
+      <c r="H4" s="303"/>
+      <c r="I4" s="303"/>
+      <c r="J4" s="303"/>
+      <c r="K4" s="304"/>
+    </row>
+    <row r="5" spans="1:11" ht="105.75">
+      <c r="A5" s="234" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="303" t="s">
+      <c r="B5" s="235" t="s">
         <v>218</v>
       </c>
-      <c r="C5" s="304" t="s">
+      <c r="C5" s="236" t="s">
         <v>219</v>
       </c>
-      <c r="D5" s="304" t="s">
+      <c r="D5" s="236" t="s">
         <v>220</v>
       </c>
-      <c r="E5" s="304" t="s">
+      <c r="E5" s="236" t="s">
         <v>221</v>
       </c>
-      <c r="F5" s="304" t="s">
+      <c r="F5" s="236" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="304" t="s">
+      <c r="G5" s="236" t="s">
         <v>223</v>
       </c>
-      <c r="H5" s="304" t="s">
+      <c r="H5" s="236" t="s">
         <v>224</v>
       </c>
-      <c r="I5" s="304" t="s">
+      <c r="I5" s="236" t="s">
         <v>225</v>
       </c>
-      <c r="J5" s="304" t="s">
+      <c r="J5" s="236" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="310" t="s">
+      <c r="K5" s="242" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="305">
+      <c r="A6" s="237">
         <v>1</v>
       </c>
-      <c r="B6" s="306" t="s">
+      <c r="B6" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="307"/>
-      <c r="D6" s="307"/>
-      <c r="E6" s="307"/>
-      <c r="F6" s="307"/>
-      <c r="G6" s="307">
+      <c r="C6" s="239"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
+      <c r="F6" s="239"/>
+      <c r="G6" s="239">
         <f>SUM(C6:F6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="307"/>
-      <c r="I6" s="307">
+      <c r="H6" s="239"/>
+      <c r="I6" s="239">
         <f>G6+H6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="307" t="str">
+      <c r="J6" s="239" t="str">
         <f>IF(I6&lt;10,"",RANK(I6,I$6:I$55))</f>
         <v/>
       </c>
-      <c r="K6" s="311" t="str">
+      <c r="K6" s="243" t="str">
         <f>IF(I6&gt;=75,"A",IF(I6&gt;=70,"B2",IF(I6&gt;=50,"C",IF(I6&gt;=45,"D",IF(I6&gt;=40,"E",IF(I6&gt;=6,"F",IF(I6&lt;5,"")))))))</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="305">
+      <c r="A7" s="237">
         <v>2</v>
       </c>
-      <c r="B7" s="306" t="s">
+      <c r="B7" s="238" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="307"/>
-      <c r="D7" s="307"/>
-      <c r="E7" s="307"/>
-      <c r="F7" s="307"/>
-      <c r="G7" s="307">
+      <c r="C7" s="239"/>
+      <c r="D7" s="239"/>
+      <c r="E7" s="239"/>
+      <c r="F7" s="239"/>
+      <c r="G7" s="239">
         <f t="shared" ref="G7:G55" si="0">SUM(C7:F7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="307"/>
-      <c r="I7" s="307">
+      <c r="H7" s="239"/>
+      <c r="I7" s="239">
         <f t="shared" ref="I7:I55" si="1">G7+H7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="307" t="str">
+      <c r="J7" s="239" t="str">
         <f t="shared" ref="J7:J55" si="2">IF(I7&lt;10,"",RANK(I7,I$6:I$55))</f>
         <v/>
       </c>
-      <c r="K7" s="311" t="str">
+      <c r="K7" s="243" t="str">
         <f t="shared" ref="K7:K55" si="3">IF(I7&gt;=75,"A",IF(I7&gt;=70,"B2",IF(I7&gt;=50,"C",IF(I7&gt;=45,"D",IF(I7&gt;=40,"E",IF(I7&gt;=6,"F",IF(I7&lt;5,"")))))))</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="305">
+      <c r="A8" s="237">
         <v>3</v>
       </c>
-      <c r="B8" s="306" t="s">
+      <c r="B8" s="238" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="307"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="307"/>
-      <c r="F8" s="307"/>
-      <c r="G8" s="307">
+      <c r="C8" s="239"/>
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
+      <c r="F8" s="239"/>
+      <c r="G8" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="307"/>
-      <c r="I8" s="307">
+      <c r="H8" s="239"/>
+      <c r="I8" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="307" t="str">
+      <c r="J8" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K8" s="311" t="str">
+      <c r="K8" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="305">
+      <c r="A9" s="237">
         <v>4</v>
       </c>
-      <c r="B9" s="306" t="s">
+      <c r="B9" s="238" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="307"/>
-      <c r="D9" s="307"/>
-      <c r="E9" s="307"/>
-      <c r="F9" s="307"/>
-      <c r="G9" s="307">
+      <c r="C9" s="239"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="307"/>
-      <c r="I9" s="307">
+      <c r="H9" s="239"/>
+      <c r="I9" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="307" t="str">
+      <c r="J9" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K9" s="311" t="str">
+      <c r="K9" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="305">
+      <c r="A10" s="237">
         <v>5</v>
       </c>
-      <c r="B10" s="306" t="s">
+      <c r="B10" s="238" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="307"/>
-      <c r="D10" s="307"/>
-      <c r="E10" s="307"/>
-      <c r="F10" s="307"/>
-      <c r="G10" s="307">
+      <c r="C10" s="239"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="307"/>
-      <c r="I10" s="307">
+      <c r="H10" s="239"/>
+      <c r="I10" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="307" t="str">
+      <c r="J10" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K10" s="311" t="str">
+      <c r="K10" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="305">
+      <c r="A11" s="237">
         <v>6</v>
       </c>
-      <c r="B11" s="306" t="s">
+      <c r="B11" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="307"/>
-      <c r="D11" s="307"/>
-      <c r="E11" s="307"/>
-      <c r="F11" s="307"/>
-      <c r="G11" s="307">
+      <c r="C11" s="239"/>
+      <c r="D11" s="239"/>
+      <c r="E11" s="239"/>
+      <c r="F11" s="239"/>
+      <c r="G11" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="307"/>
-      <c r="I11" s="307">
+      <c r="H11" s="239"/>
+      <c r="I11" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="307" t="str">
+      <c r="J11" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K11" s="311" t="str">
+      <c r="K11" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="305">
+      <c r="A12" s="237">
         <v>7</v>
       </c>
-      <c r="B12" s="306" t="s">
+      <c r="B12" s="238" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="307"/>
-      <c r="D12" s="307"/>
-      <c r="E12" s="307"/>
-      <c r="F12" s="307"/>
-      <c r="G12" s="307">
+      <c r="C12" s="239"/>
+      <c r="D12" s="239"/>
+      <c r="E12" s="239"/>
+      <c r="F12" s="239"/>
+      <c r="G12" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="307"/>
-      <c r="I12" s="307">
+      <c r="H12" s="239"/>
+      <c r="I12" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="307" t="str">
+      <c r="J12" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K12" s="311" t="str">
+      <c r="K12" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="305">
+      <c r="A13" s="237">
         <v>8</v>
       </c>
-      <c r="B13" s="306" t="s">
+      <c r="B13" s="238" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="307"/>
-      <c r="D13" s="307"/>
-      <c r="E13" s="307"/>
-      <c r="F13" s="307"/>
-      <c r="G13" s="307">
+      <c r="C13" s="239"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="239"/>
+      <c r="G13" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="307"/>
-      <c r="I13" s="307">
+      <c r="H13" s="239"/>
+      <c r="I13" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="307" t="str">
+      <c r="J13" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K13" s="311" t="str">
+      <c r="K13" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="305">
+      <c r="A14" s="237">
         <v>9</v>
       </c>
-      <c r="B14" s="306" t="s">
+      <c r="B14" s="238" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="307"/>
-      <c r="D14" s="307"/>
-      <c r="E14" s="307"/>
-      <c r="F14" s="307"/>
-      <c r="G14" s="307">
+      <c r="C14" s="239"/>
+      <c r="D14" s="239"/>
+      <c r="E14" s="239"/>
+      <c r="F14" s="239"/>
+      <c r="G14" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="307"/>
-      <c r="I14" s="307">
+      <c r="H14" s="239"/>
+      <c r="I14" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="307" t="str">
+      <c r="J14" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K14" s="311" t="str">
+      <c r="K14" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="305">
-        <v>10</v>
-      </c>
-      <c r="B15" s="306" t="s">
+      <c r="A15" s="237">
+        <v>10</v>
+      </c>
+      <c r="B15" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="307"/>
-      <c r="D15" s="307"/>
-      <c r="E15" s="307"/>
-      <c r="F15" s="307"/>
-      <c r="G15" s="307">
+      <c r="C15" s="239"/>
+      <c r="D15" s="239"/>
+      <c r="E15" s="239"/>
+      <c r="F15" s="239"/>
+      <c r="G15" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="307"/>
-      <c r="I15" s="307">
+      <c r="H15" s="239"/>
+      <c r="I15" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="307" t="str">
+      <c r="J15" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K15" s="311" t="str">
+      <c r="K15" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="305">
+      <c r="A16" s="237">
         <v>11</v>
       </c>
-      <c r="B16" s="306" t="s">
+      <c r="B16" s="238" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="307"/>
-      <c r="D16" s="307"/>
-      <c r="E16" s="307"/>
-      <c r="F16" s="307"/>
-      <c r="G16" s="307">
+      <c r="C16" s="239"/>
+      <c r="D16" s="239"/>
+      <c r="E16" s="239"/>
+      <c r="F16" s="239"/>
+      <c r="G16" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="307"/>
-      <c r="I16" s="307">
+      <c r="H16" s="239"/>
+      <c r="I16" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="307" t="str">
+      <c r="J16" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K16" s="311" t="str">
+      <c r="K16" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="305">
+      <c r="A17" s="237">
         <v>12</v>
       </c>
-      <c r="B17" s="306" t="s">
+      <c r="B17" s="238" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="307"/>
-      <c r="D17" s="307"/>
-      <c r="E17" s="307"/>
-      <c r="F17" s="307"/>
-      <c r="G17" s="307">
+      <c r="C17" s="239"/>
+      <c r="D17" s="239"/>
+      <c r="E17" s="239"/>
+      <c r="F17" s="239"/>
+      <c r="G17" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="307"/>
-      <c r="I17" s="307">
+      <c r="H17" s="239"/>
+      <c r="I17" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="307" t="str">
+      <c r="J17" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K17" s="311" t="str">
+      <c r="K17" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="305">
+      <c r="A18" s="237">
         <v>13</v>
       </c>
-      <c r="B18" s="306" t="s">
+      <c r="B18" s="238" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="307"/>
-      <c r="D18" s="307"/>
-      <c r="E18" s="307"/>
-      <c r="F18" s="307"/>
-      <c r="G18" s="307">
+      <c r="C18" s="239"/>
+      <c r="D18" s="239"/>
+      <c r="E18" s="239"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="307"/>
-      <c r="I18" s="307">
+      <c r="H18" s="239"/>
+      <c r="I18" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="307" t="str">
+      <c r="J18" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K18" s="311" t="str">
+      <c r="K18" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="305">
+      <c r="A19" s="237">
         <v>14</v>
       </c>
-      <c r="B19" s="306" t="s">
+      <c r="B19" s="238" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="307"/>
-      <c r="D19" s="307"/>
-      <c r="E19" s="307"/>
-      <c r="F19" s="307"/>
-      <c r="G19" s="307">
+      <c r="C19" s="239"/>
+      <c r="D19" s="239"/>
+      <c r="E19" s="239"/>
+      <c r="F19" s="239"/>
+      <c r="G19" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="307"/>
-      <c r="I19" s="307">
+      <c r="H19" s="239"/>
+      <c r="I19" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="307" t="str">
+      <c r="J19" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K19" s="311" t="str">
+      <c r="K19" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="305">
+      <c r="A20" s="237">
         <v>15</v>
       </c>
-      <c r="B20" s="306" t="s">
+      <c r="B20" s="238" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="307"/>
-      <c r="D20" s="307"/>
-      <c r="E20" s="307"/>
-      <c r="F20" s="307"/>
-      <c r="G20" s="307">
+      <c r="C20" s="239"/>
+      <c r="D20" s="239"/>
+      <c r="E20" s="239"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="307"/>
-      <c r="I20" s="307">
+      <c r="H20" s="239"/>
+      <c r="I20" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="307" t="str">
+      <c r="J20" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K20" s="311" t="str">
+      <c r="K20" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="305">
+      <c r="A21" s="237">
         <v>16</v>
       </c>
-      <c r="B21" s="306" t="s">
+      <c r="B21" s="238" t="s">
         <v>213</v>
       </c>
-      <c r="C21" s="307"/>
-      <c r="D21" s="307"/>
-      <c r="E21" s="307"/>
-      <c r="F21" s="307"/>
-      <c r="G21" s="307">
+      <c r="C21" s="239"/>
+      <c r="D21" s="239"/>
+      <c r="E21" s="239"/>
+      <c r="F21" s="239"/>
+      <c r="G21" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="307"/>
-      <c r="I21" s="307">
+      <c r="H21" s="239"/>
+      <c r="I21" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="307" t="str">
+      <c r="J21" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K21" s="311" t="str">
+      <c r="K21" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="305">
+      <c r="A22" s="237">
         <v>17</v>
       </c>
-      <c r="B22" s="306" t="s">
+      <c r="B22" s="238" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="307"/>
-      <c r="D22" s="307"/>
-      <c r="E22" s="307"/>
-      <c r="F22" s="307"/>
-      <c r="G22" s="307">
+      <c r="C22" s="239"/>
+      <c r="D22" s="239"/>
+      <c r="E22" s="239"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="307"/>
-      <c r="I22" s="307">
+      <c r="H22" s="239"/>
+      <c r="I22" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="307" t="str">
+      <c r="J22" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K22" s="311" t="str">
+      <c r="K22" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="305">
+      <c r="A23" s="237">
         <v>18</v>
       </c>
-      <c r="B23" s="306" t="s">
+      <c r="B23" s="238" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="307"/>
-      <c r="D23" s="307"/>
-      <c r="E23" s="307"/>
-      <c r="F23" s="307"/>
-      <c r="G23" s="307">
+      <c r="C23" s="239"/>
+      <c r="D23" s="239"/>
+      <c r="E23" s="239"/>
+      <c r="F23" s="239"/>
+      <c r="G23" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="307"/>
-      <c r="I23" s="307">
+      <c r="H23" s="239"/>
+      <c r="I23" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="307" t="str">
+      <c r="J23" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K23" s="311" t="str">
+      <c r="K23" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="305">
+      <c r="A24" s="237">
         <v>19</v>
       </c>
-      <c r="B24" s="306" t="s">
+      <c r="B24" s="238" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="307"/>
-      <c r="D24" s="307"/>
-      <c r="E24" s="307"/>
-      <c r="F24" s="307"/>
-      <c r="G24" s="307">
+      <c r="C24" s="239"/>
+      <c r="D24" s="239"/>
+      <c r="E24" s="239"/>
+      <c r="F24" s="239"/>
+      <c r="G24" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="307"/>
-      <c r="I24" s="307">
+      <c r="H24" s="239"/>
+      <c r="I24" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="307" t="str">
+      <c r="J24" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K24" s="311" t="str">
+      <c r="K24" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="305">
+      <c r="A25" s="237">
         <v>20</v>
       </c>
-      <c r="B25" s="306" t="s">
+      <c r="B25" s="238" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="307"/>
-      <c r="D25" s="307"/>
-      <c r="E25" s="307"/>
-      <c r="F25" s="307"/>
-      <c r="G25" s="307">
+      <c r="C25" s="239"/>
+      <c r="D25" s="239"/>
+      <c r="E25" s="239"/>
+      <c r="F25" s="239"/>
+      <c r="G25" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="307"/>
-      <c r="I25" s="307">
+      <c r="H25" s="239"/>
+      <c r="I25" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J25" s="307" t="str">
+      <c r="J25" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K25" s="311" t="str">
+      <c r="K25" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="305">
+      <c r="A26" s="237">
         <v>21</v>
       </c>
-      <c r="B26" s="306" t="s">
+      <c r="B26" s="238" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="307"/>
-      <c r="D26" s="307"/>
-      <c r="E26" s="307"/>
-      <c r="F26" s="307"/>
-      <c r="G26" s="307">
+      <c r="C26" s="239"/>
+      <c r="D26" s="239"/>
+      <c r="E26" s="239"/>
+      <c r="F26" s="239"/>
+      <c r="G26" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H26" s="307"/>
-      <c r="I26" s="307">
+      <c r="H26" s="239"/>
+      <c r="I26" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="307" t="str">
+      <c r="J26" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K26" s="311" t="str">
+      <c r="K26" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="305">
+      <c r="A27" s="237">
         <v>22</v>
       </c>
-      <c r="B27" s="306" t="s">
+      <c r="B27" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="307"/>
-      <c r="D27" s="307"/>
-      <c r="E27" s="307"/>
-      <c r="F27" s="307"/>
-      <c r="G27" s="307">
+      <c r="C27" s="239"/>
+      <c r="D27" s="239"/>
+      <c r="E27" s="239"/>
+      <c r="F27" s="239"/>
+      <c r="G27" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H27" s="307"/>
-      <c r="I27" s="307">
+      <c r="H27" s="239"/>
+      <c r="I27" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="307" t="str">
+      <c r="J27" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K27" s="311" t="str">
+      <c r="K27" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="305">
+      <c r="A28" s="237">
         <v>23</v>
       </c>
-      <c r="B28" s="306" t="s">
+      <c r="B28" s="238" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="307"/>
-      <c r="D28" s="307"/>
-      <c r="E28" s="307"/>
-      <c r="F28" s="307"/>
-      <c r="G28" s="307">
+      <c r="C28" s="239"/>
+      <c r="D28" s="239"/>
+      <c r="E28" s="239"/>
+      <c r="F28" s="239"/>
+      <c r="G28" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H28" s="307"/>
-      <c r="I28" s="307">
+      <c r="H28" s="239"/>
+      <c r="I28" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="307" t="str">
+      <c r="J28" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K28" s="311" t="str">
+      <c r="K28" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="305">
+      <c r="A29" s="237">
         <v>24</v>
       </c>
-      <c r="B29" s="306" t="s">
+      <c r="B29" s="238" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="307"/>
-      <c r="D29" s="307"/>
-      <c r="E29" s="307"/>
-      <c r="F29" s="307"/>
-      <c r="G29" s="307">
+      <c r="C29" s="239"/>
+      <c r="D29" s="239"/>
+      <c r="E29" s="239"/>
+      <c r="F29" s="239"/>
+      <c r="G29" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H29" s="307"/>
-      <c r="I29" s="307">
+      <c r="H29" s="239"/>
+      <c r="I29" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="307" t="str">
+      <c r="J29" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K29" s="311" t="str">
+      <c r="K29" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="305">
+      <c r="A30" s="237">
         <v>25</v>
       </c>
-      <c r="B30" s="306" t="s">
+      <c r="B30" s="238" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="307"/>
-      <c r="D30" s="307"/>
-      <c r="E30" s="307"/>
-      <c r="F30" s="307"/>
-      <c r="G30" s="307">
+      <c r="C30" s="239"/>
+      <c r="D30" s="239"/>
+      <c r="E30" s="239"/>
+      <c r="F30" s="239"/>
+      <c r="G30" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H30" s="307"/>
-      <c r="I30" s="307">
+      <c r="H30" s="239"/>
+      <c r="I30" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J30" s="307" t="str">
+      <c r="J30" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K30" s="311" t="str">
+      <c r="K30" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="305">
+      <c r="A31" s="237">
         <v>26</v>
       </c>
-      <c r="B31" s="306" t="s">
+      <c r="B31" s="238" t="s">
         <v>186</v>
       </c>
-      <c r="C31" s="307"/>
-      <c r="D31" s="307"/>
-      <c r="E31" s="307"/>
-      <c r="F31" s="307"/>
-      <c r="G31" s="307">
+      <c r="C31" s="239"/>
+      <c r="D31" s="239"/>
+      <c r="E31" s="239"/>
+      <c r="F31" s="239"/>
+      <c r="G31" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H31" s="307"/>
-      <c r="I31" s="307">
+      <c r="H31" s="239"/>
+      <c r="I31" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="307" t="str">
+      <c r="J31" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K31" s="311" t="str">
+      <c r="K31" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="305">
+      <c r="A32" s="237">
         <v>27</v>
       </c>
-      <c r="B32" s="306" t="s">
+      <c r="B32" s="238" t="s">
         <v>126</v>
       </c>
-      <c r="C32" s="307"/>
-      <c r="D32" s="307"/>
-      <c r="E32" s="307"/>
-      <c r="F32" s="307"/>
-      <c r="G32" s="307">
+      <c r="C32" s="239"/>
+      <c r="D32" s="239"/>
+      <c r="E32" s="239"/>
+      <c r="F32" s="239"/>
+      <c r="G32" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H32" s="307"/>
-      <c r="I32" s="307">
+      <c r="H32" s="239"/>
+      <c r="I32" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="307" t="str">
+      <c r="J32" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K32" s="311" t="str">
+      <c r="K32" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="305">
+      <c r="A33" s="237">
         <v>28</v>
       </c>
-      <c r="B33" s="306" t="s">
+      <c r="B33" s="238" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="307"/>
-      <c r="D33" s="307"/>
-      <c r="E33" s="307"/>
-      <c r="F33" s="307"/>
-      <c r="G33" s="307">
+      <c r="C33" s="239"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="239"/>
+      <c r="F33" s="239"/>
+      <c r="G33" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="307"/>
-      <c r="I33" s="307">
+      <c r="H33" s="239"/>
+      <c r="I33" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="307" t="str">
+      <c r="J33" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K33" s="311" t="str">
+      <c r="K33" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="305">
+      <c r="A34" s="237">
         <v>29</v>
       </c>
-      <c r="B34" s="306" t="s">
+      <c r="B34" s="238" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="307"/>
-      <c r="D34" s="307"/>
-      <c r="E34" s="307"/>
-      <c r="F34" s="307"/>
-      <c r="G34" s="307">
+      <c r="C34" s="239"/>
+      <c r="D34" s="239"/>
+      <c r="E34" s="239"/>
+      <c r="F34" s="239"/>
+      <c r="G34" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H34" s="307"/>
-      <c r="I34" s="307">
+      <c r="H34" s="239"/>
+      <c r="I34" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="307" t="str">
+      <c r="J34" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K34" s="311" t="str">
+      <c r="K34" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="305">
+      <c r="A35" s="237">
         <v>30</v>
       </c>
-      <c r="B35" s="306" t="s">
+      <c r="B35" s="238" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="307"/>
-      <c r="D35" s="307"/>
-      <c r="E35" s="307"/>
-      <c r="F35" s="307"/>
-      <c r="G35" s="307">
+      <c r="C35" s="239"/>
+      <c r="D35" s="239"/>
+      <c r="E35" s="239"/>
+      <c r="F35" s="239"/>
+      <c r="G35" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H35" s="307"/>
-      <c r="I35" s="307">
+      <c r="H35" s="239"/>
+      <c r="I35" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="307" t="str">
+      <c r="J35" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K35" s="311" t="str">
+      <c r="K35" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="305">
+      <c r="A36" s="237">
         <v>31</v>
       </c>
-      <c r="B36" s="306" t="s">
+      <c r="B36" s="238" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="307"/>
-      <c r="D36" s="307"/>
-      <c r="E36" s="307"/>
-      <c r="F36" s="307"/>
-      <c r="G36" s="307">
+      <c r="C36" s="239"/>
+      <c r="D36" s="239"/>
+      <c r="E36" s="239"/>
+      <c r="F36" s="239"/>
+      <c r="G36" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H36" s="307"/>
-      <c r="I36" s="307">
+      <c r="H36" s="239"/>
+      <c r="I36" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J36" s="307" t="str">
+      <c r="J36" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K36" s="311" t="str">
+      <c r="K36" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="305">
+      <c r="A37" s="237">
         <v>32</v>
       </c>
-      <c r="B37" s="306" t="s">
+      <c r="B37" s="238" t="s">
         <v>131</v>
       </c>
-      <c r="C37" s="307"/>
-      <c r="D37" s="307"/>
-      <c r="E37" s="307"/>
-      <c r="F37" s="307"/>
-      <c r="G37" s="307">
+      <c r="C37" s="239"/>
+      <c r="D37" s="239"/>
+      <c r="E37" s="239"/>
+      <c r="F37" s="239"/>
+      <c r="G37" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H37" s="307"/>
-      <c r="I37" s="307">
+      <c r="H37" s="239"/>
+      <c r="I37" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="307" t="str">
+      <c r="J37" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="311" t="str">
+      <c r="K37" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="305">
+      <c r="A38" s="237">
         <v>33</v>
       </c>
-      <c r="B38" s="306" t="s">
+      <c r="B38" s="238" t="s">
         <v>132</v>
       </c>
-      <c r="C38" s="307"/>
-      <c r="D38" s="307"/>
-      <c r="E38" s="307"/>
-      <c r="F38" s="307"/>
-      <c r="G38" s="307">
+      <c r="C38" s="239"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="239"/>
+      <c r="F38" s="239"/>
+      <c r="G38" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H38" s="307"/>
-      <c r="I38" s="307">
+      <c r="H38" s="239"/>
+      <c r="I38" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J38" s="307" t="str">
+      <c r="J38" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K38" s="311" t="str">
+      <c r="K38" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="305">
+      <c r="A39" s="237">
         <v>34</v>
       </c>
-      <c r="B39" s="306" t="s">
+      <c r="B39" s="238" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="307"/>
-      <c r="D39" s="307"/>
-      <c r="E39" s="307"/>
-      <c r="F39" s="307"/>
-      <c r="G39" s="307">
+      <c r="C39" s="239"/>
+      <c r="D39" s="239"/>
+      <c r="E39" s="239"/>
+      <c r="F39" s="239"/>
+      <c r="G39" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H39" s="307"/>
-      <c r="I39" s="307">
+      <c r="H39" s="239"/>
+      <c r="I39" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J39" s="307" t="str">
+      <c r="J39" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K39" s="311" t="str">
+      <c r="K39" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="305">
+      <c r="A40" s="237">
         <v>35</v>
       </c>
-      <c r="B40" s="306" t="s">
+      <c r="B40" s="238" t="s">
         <v>134</v>
       </c>
-      <c r="C40" s="307"/>
-      <c r="D40" s="307"/>
-      <c r="E40" s="307"/>
-      <c r="F40" s="307"/>
-      <c r="G40" s="307">
+      <c r="C40" s="239"/>
+      <c r="D40" s="239"/>
+      <c r="E40" s="239"/>
+      <c r="F40" s="239"/>
+      <c r="G40" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H40" s="307"/>
-      <c r="I40" s="307">
+      <c r="H40" s="239"/>
+      <c r="I40" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J40" s="307" t="str">
+      <c r="J40" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K40" s="311" t="str">
+      <c r="K40" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="305">
+      <c r="A41" s="237">
         <v>36</v>
       </c>
-      <c r="B41" s="306" t="s">
+      <c r="B41" s="238" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="307"/>
-      <c r="D41" s="307"/>
-      <c r="E41" s="307"/>
-      <c r="F41" s="307"/>
-      <c r="G41" s="307">
+      <c r="C41" s="239"/>
+      <c r="D41" s="239"/>
+      <c r="E41" s="239"/>
+      <c r="F41" s="239"/>
+      <c r="G41" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H41" s="307"/>
-      <c r="I41" s="307">
+      <c r="H41" s="239"/>
+      <c r="I41" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J41" s="307" t="str">
+      <c r="J41" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K41" s="311" t="str">
+      <c r="K41" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="305">
+      <c r="A42" s="237">
         <v>37</v>
       </c>
-      <c r="B42" s="306" t="s">
+      <c r="B42" s="238" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="307"/>
-      <c r="D42" s="307"/>
-      <c r="E42" s="307"/>
-      <c r="F42" s="307"/>
-      <c r="G42" s="307">
+      <c r="C42" s="239"/>
+      <c r="D42" s="239"/>
+      <c r="E42" s="239"/>
+      <c r="F42" s="239"/>
+      <c r="G42" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H42" s="307"/>
-      <c r="I42" s="307">
+      <c r="H42" s="239"/>
+      <c r="I42" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J42" s="307" t="str">
+      <c r="J42" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K42" s="311" t="str">
+      <c r="K42" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="305">
+      <c r="A43" s="237">
         <v>38</v>
       </c>
-      <c r="B43" s="306" t="s">
+      <c r="B43" s="238" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="307"/>
-      <c r="D43" s="307"/>
-      <c r="E43" s="307"/>
-      <c r="F43" s="307"/>
-      <c r="G43" s="307">
+      <c r="C43" s="239"/>
+      <c r="D43" s="239"/>
+      <c r="E43" s="239"/>
+      <c r="F43" s="239"/>
+      <c r="G43" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H43" s="307"/>
-      <c r="I43" s="307">
+      <c r="H43" s="239"/>
+      <c r="I43" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J43" s="307" t="str">
+      <c r="J43" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K43" s="311" t="str">
+      <c r="K43" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="305">
+      <c r="A44" s="237">
         <v>39</v>
       </c>
-      <c r="B44" s="306" t="s">
+      <c r="B44" s="238" t="s">
         <v>203</v>
       </c>
-      <c r="C44" s="307"/>
-      <c r="D44" s="307"/>
-      <c r="E44" s="307"/>
-      <c r="F44" s="307"/>
-      <c r="G44" s="307">
+      <c r="C44" s="239"/>
+      <c r="D44" s="239"/>
+      <c r="E44" s="239"/>
+      <c r="F44" s="239"/>
+      <c r="G44" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H44" s="307"/>
-      <c r="I44" s="307">
+      <c r="H44" s="239"/>
+      <c r="I44" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J44" s="307" t="str">
+      <c r="J44" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K44" s="311" t="str">
+      <c r="K44" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="305">
+      <c r="A45" s="237">
         <v>40</v>
       </c>
-      <c r="B45" s="306" t="s">
+      <c r="B45" s="238" t="s">
         <v>204</v>
       </c>
-      <c r="C45" s="307"/>
-      <c r="D45" s="307"/>
-      <c r="E45" s="307"/>
-      <c r="F45" s="307"/>
-      <c r="G45" s="307">
+      <c r="C45" s="239"/>
+      <c r="D45" s="239"/>
+      <c r="E45" s="239"/>
+      <c r="F45" s="239"/>
+      <c r="G45" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H45" s="307"/>
-      <c r="I45" s="307">
+      <c r="H45" s="239"/>
+      <c r="I45" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J45" s="307" t="str">
+      <c r="J45" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K45" s="311" t="str">
+      <c r="K45" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="305">
+      <c r="A46" s="237">
         <v>41</v>
       </c>
       <c r="B46" s="17"/>
-      <c r="C46" s="307"/>
-      <c r="D46" s="307"/>
-      <c r="E46" s="307"/>
-      <c r="F46" s="307"/>
-      <c r="G46" s="307">
+      <c r="C46" s="239"/>
+      <c r="D46" s="239"/>
+      <c r="E46" s="239"/>
+      <c r="F46" s="239"/>
+      <c r="G46" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H46" s="307"/>
-      <c r="I46" s="307">
+      <c r="H46" s="239"/>
+      <c r="I46" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J46" s="307" t="str">
+      <c r="J46" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K46" s="311" t="str">
+      <c r="K46" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="305">
+      <c r="A47" s="237">
         <v>42</v>
       </c>
-      <c r="B47" s="306"/>
-      <c r="C47" s="307"/>
-      <c r="D47" s="307"/>
-      <c r="E47" s="307"/>
-      <c r="F47" s="307"/>
-      <c r="G47" s="307">
+      <c r="B47" s="238"/>
+      <c r="C47" s="239"/>
+      <c r="D47" s="239"/>
+      <c r="E47" s="239"/>
+      <c r="F47" s="239"/>
+      <c r="G47" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H47" s="307"/>
-      <c r="I47" s="307">
+      <c r="H47" s="239"/>
+      <c r="I47" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J47" s="307" t="str">
+      <c r="J47" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K47" s="311" t="str">
+      <c r="K47" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="305">
+      <c r="A48" s="237">
         <v>43</v>
       </c>
-      <c r="B48" s="306"/>
-      <c r="C48" s="307"/>
-      <c r="D48" s="307"/>
-      <c r="E48" s="307"/>
-      <c r="F48" s="307"/>
-      <c r="G48" s="307">
+      <c r="B48" s="238"/>
+      <c r="C48" s="239"/>
+      <c r="D48" s="239"/>
+      <c r="E48" s="239"/>
+      <c r="F48" s="239"/>
+      <c r="G48" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H48" s="307"/>
-      <c r="I48" s="307">
+      <c r="H48" s="239"/>
+      <c r="I48" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J48" s="307" t="str">
+      <c r="J48" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K48" s="311" t="str">
+      <c r="K48" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="305">
+      <c r="A49" s="237">
         <v>44</v>
       </c>
-      <c r="B49" s="306"/>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="307"/>
-      <c r="G49" s="307">
+      <c r="B49" s="238"/>
+      <c r="C49" s="239"/>
+      <c r="D49" s="239"/>
+      <c r="E49" s="239"/>
+      <c r="F49" s="239"/>
+      <c r="G49" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H49" s="307"/>
-      <c r="I49" s="307">
+      <c r="H49" s="239"/>
+      <c r="I49" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J49" s="307" t="str">
+      <c r="J49" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K49" s="311" t="str">
+      <c r="K49" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="305">
+      <c r="A50" s="237">
         <v>45</v>
       </c>
-      <c r="B50" s="307"/>
-      <c r="C50" s="307"/>
-      <c r="D50" s="307"/>
-      <c r="E50" s="307"/>
-      <c r="F50" s="307"/>
-      <c r="G50" s="307">
+      <c r="B50" s="239"/>
+      <c r="C50" s="239"/>
+      <c r="D50" s="239"/>
+      <c r="E50" s="239"/>
+      <c r="F50" s="239"/>
+      <c r="G50" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H50" s="307"/>
-      <c r="I50" s="307">
+      <c r="H50" s="239"/>
+      <c r="I50" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J50" s="307" t="str">
+      <c r="J50" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K50" s="311" t="str">
+      <c r="K50" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="305">
+      <c r="A51" s="237">
         <v>46</v>
       </c>
-      <c r="B51" s="307"/>
-      <c r="C51" s="307"/>
-      <c r="D51" s="307"/>
-      <c r="E51" s="307"/>
-      <c r="F51" s="307"/>
-      <c r="G51" s="307">
+      <c r="B51" s="239"/>
+      <c r="C51" s="239"/>
+      <c r="D51" s="239"/>
+      <c r="E51" s="239"/>
+      <c r="F51" s="239"/>
+      <c r="G51" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H51" s="307"/>
-      <c r="I51" s="307">
+      <c r="H51" s="239"/>
+      <c r="I51" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J51" s="307" t="str">
+      <c r="J51" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K51" s="311" t="str">
+      <c r="K51" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="305">
+      <c r="A52" s="237">
         <v>47</v>
       </c>
-      <c r="B52" s="307"/>
-      <c r="C52" s="307"/>
-      <c r="D52" s="307"/>
-      <c r="E52" s="307"/>
-      <c r="F52" s="307"/>
-      <c r="G52" s="307">
+      <c r="B52" s="239"/>
+      <c r="C52" s="239"/>
+      <c r="D52" s="239"/>
+      <c r="E52" s="239"/>
+      <c r="F52" s="239"/>
+      <c r="G52" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H52" s="307"/>
-      <c r="I52" s="307">
+      <c r="H52" s="239"/>
+      <c r="I52" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J52" s="307" t="str">
+      <c r="J52" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K52" s="311" t="str">
+      <c r="K52" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="305">
+      <c r="A53" s="237">
         <v>48</v>
       </c>
-      <c r="B53" s="307"/>
-      <c r="C53" s="307"/>
-      <c r="D53" s="307"/>
-      <c r="E53" s="307"/>
-      <c r="F53" s="307"/>
-      <c r="G53" s="307">
+      <c r="B53" s="239"/>
+      <c r="C53" s="239"/>
+      <c r="D53" s="239"/>
+      <c r="E53" s="239"/>
+      <c r="F53" s="239"/>
+      <c r="G53" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H53" s="307"/>
-      <c r="I53" s="307">
+      <c r="H53" s="239"/>
+      <c r="I53" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J53" s="307" t="str">
+      <c r="J53" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K53" s="311" t="str">
+      <c r="K53" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="305">
+      <c r="A54" s="237">
         <v>49</v>
       </c>
-      <c r="B54" s="307"/>
-      <c r="C54" s="307"/>
-      <c r="D54" s="307"/>
-      <c r="E54" s="307"/>
-      <c r="F54" s="307"/>
-      <c r="G54" s="307">
+      <c r="B54" s="239"/>
+      <c r="C54" s="239"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="239"/>
+      <c r="F54" s="239"/>
+      <c r="G54" s="239">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H54" s="307"/>
-      <c r="I54" s="307">
+      <c r="H54" s="239"/>
+      <c r="I54" s="239">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J54" s="307" t="str">
+      <c r="J54" s="239" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K54" s="311" t="str">
+      <c r="K54" s="243" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A55" s="308">
+      <c r="A55" s="240">
         <v>50</v>
       </c>
-      <c r="B55" s="309"/>
-      <c r="C55" s="309"/>
-      <c r="D55" s="309"/>
-      <c r="E55" s="309"/>
-      <c r="F55" s="309"/>
-      <c r="G55" s="309">
+      <c r="B55" s="241"/>
+      <c r="C55" s="241"/>
+      <c r="D55" s="241"/>
+      <c r="E55" s="241"/>
+      <c r="F55" s="241"/>
+      <c r="G55" s="241">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H55" s="309"/>
-      <c r="I55" s="309">
+      <c r="H55" s="241"/>
+      <c r="I55" s="241">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J55" s="309" t="str">
+      <c r="J55" s="241" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K55" s="312" t="str">
+      <c r="K55" s="244" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -47099,7 +47104,7 @@
     <col min="21" max="22" width="11.140625" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="75">
+    <row r="1" spans="1:22" ht="74.25">
       <c r="A1" s="88" t="s">
         <v>150</v>
       </c>

--- a/Report JSS 1G.xlsx
+++ b/Report JSS 1G.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -2190,23 +2190,23 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2223,23 +2223,72 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2268,55 +2317,6 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3303,7 +3303,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3394,7 +3394,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3490,7 +3490,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9481,14 +9481,14 @@
     </row>
     <row r="2" spans="1:216">
       <c r="A2" s="126"/>
-      <c r="B2" s="256" t="s">
+      <c r="B2" s="245" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="256"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
       <c r="H2" s="127"/>
       <c r="I2" s="127"/>
       <c r="J2" s="128"/>
@@ -9497,28 +9497,28 @@
       <c r="M2" s="126"/>
       <c r="N2" s="129"/>
       <c r="O2" s="113"/>
-      <c r="P2" s="259" t="s">
+      <c r="P2" s="249" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="260"/>
-      <c r="T2" s="260"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="260"/>
+      <c r="Q2" s="250"/>
+      <c r="R2" s="250"/>
+      <c r="S2" s="250"/>
+      <c r="T2" s="250"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="250"/>
       <c r="W2" s="130"/>
       <c r="X2" s="130"/>
       <c r="Y2" s="131"/>
       <c r="Z2" s="132"/>
-      <c r="AA2" s="250" t="s">
+      <c r="AA2" s="246" t="s">
         <v>98</v>
       </c>
-      <c r="AB2" s="250"/>
-      <c r="AC2" s="250"/>
-      <c r="AD2" s="250"/>
-      <c r="AE2" s="250"/>
-      <c r="AF2" s="250"/>
-      <c r="AG2" s="250"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
+      <c r="AD2" s="246"/>
+      <c r="AE2" s="246"/>
+      <c r="AF2" s="246"/>
+      <c r="AG2" s="246"/>
       <c r="AH2" s="132"/>
       <c r="AI2" s="132"/>
       <c r="AJ2" s="132"/>
@@ -9538,29 +9538,29 @@
       <c r="AV2" s="133"/>
       <c r="AW2" s="111"/>
       <c r="AX2" s="45"/>
-      <c r="AY2" s="257" t="s">
+      <c r="AY2" s="247" t="s">
         <v>93</v>
       </c>
-      <c r="AZ2" s="257"/>
-      <c r="BA2" s="257"/>
-      <c r="BB2" s="257"/>
-      <c r="BC2" s="257"/>
-      <c r="BD2" s="257"/>
-      <c r="BE2" s="257"/>
+      <c r="AZ2" s="247"/>
+      <c r="BA2" s="247"/>
+      <c r="BB2" s="247"/>
+      <c r="BC2" s="247"/>
+      <c r="BD2" s="247"/>
+      <c r="BE2" s="247"/>
       <c r="BF2" s="45"/>
       <c r="BG2" s="45"/>
       <c r="BH2" s="45"/>
       <c r="BI2" s="111"/>
       <c r="BJ2" s="135"/>
-      <c r="BK2" s="258" t="s">
+      <c r="BK2" s="248" t="s">
         <v>64</v>
       </c>
-      <c r="BL2" s="258"/>
-      <c r="BM2" s="258"/>
-      <c r="BN2" s="258"/>
-      <c r="BO2" s="258"/>
-      <c r="BP2" s="258"/>
-      <c r="BQ2" s="258"/>
+      <c r="BL2" s="248"/>
+      <c r="BM2" s="248"/>
+      <c r="BN2" s="248"/>
+      <c r="BO2" s="248"/>
+      <c r="BP2" s="248"/>
+      <c r="BQ2" s="248"/>
       <c r="BR2" s="135"/>
       <c r="BS2" s="135"/>
       <c r="BT2" s="135"/>
@@ -9636,99 +9636,99 @@
       <c r="EB2" s="139"/>
       <c r="EC2" s="111"/>
       <c r="ED2" s="140"/>
-      <c r="EE2" s="247" t="s">
+      <c r="EE2" s="258" t="s">
         <v>65</v>
       </c>
-      <c r="EF2" s="247"/>
-      <c r="EG2" s="247"/>
-      <c r="EH2" s="247"/>
-      <c r="EI2" s="247"/>
-      <c r="EJ2" s="247"/>
-      <c r="EK2" s="247"/>
+      <c r="EF2" s="258"/>
+      <c r="EG2" s="258"/>
+      <c r="EH2" s="258"/>
+      <c r="EI2" s="258"/>
+      <c r="EJ2" s="258"/>
+      <c r="EK2" s="258"/>
       <c r="EL2" s="140"/>
       <c r="EM2" s="140"/>
       <c r="EN2" s="140"/>
       <c r="EO2" s="111"/>
       <c r="EP2" s="141"/>
-      <c r="EQ2" s="248" t="s">
+      <c r="EQ2" s="259" t="s">
         <v>68</v>
       </c>
-      <c r="ER2" s="248"/>
-      <c r="ES2" s="248"/>
-      <c r="ET2" s="248"/>
-      <c r="EU2" s="248"/>
-      <c r="EV2" s="248"/>
-      <c r="EW2" s="248"/>
+      <c r="ER2" s="259"/>
+      <c r="ES2" s="259"/>
+      <c r="ET2" s="259"/>
+      <c r="EU2" s="259"/>
+      <c r="EV2" s="259"/>
+      <c r="EW2" s="259"/>
       <c r="EX2" s="141"/>
       <c r="EY2" s="141"/>
       <c r="EZ2" s="141"/>
       <c r="FA2" s="111"/>
       <c r="FB2" s="142"/>
-      <c r="FC2" s="246" t="s">
+      <c r="FC2" s="257" t="s">
         <v>66</v>
       </c>
-      <c r="FD2" s="246"/>
-      <c r="FE2" s="246"/>
-      <c r="FF2" s="246"/>
-      <c r="FG2" s="246"/>
-      <c r="FH2" s="246"/>
-      <c r="FI2" s="246"/>
+      <c r="FD2" s="257"/>
+      <c r="FE2" s="257"/>
+      <c r="FF2" s="257"/>
+      <c r="FG2" s="257"/>
+      <c r="FH2" s="257"/>
+      <c r="FI2" s="257"/>
       <c r="FJ2" s="142"/>
       <c r="FK2" s="142"/>
       <c r="FL2" s="142"/>
       <c r="FM2" s="111"/>
       <c r="FN2" s="128"/>
-      <c r="FO2" s="249" t="s">
+      <c r="FO2" s="260" t="s">
         <v>94</v>
       </c>
-      <c r="FP2" s="249"/>
-      <c r="FQ2" s="249"/>
-      <c r="FR2" s="249"/>
-      <c r="FS2" s="249"/>
-      <c r="FT2" s="249"/>
-      <c r="FU2" s="249"/>
+      <c r="FP2" s="260"/>
+      <c r="FQ2" s="260"/>
+      <c r="FR2" s="260"/>
+      <c r="FS2" s="260"/>
+      <c r="FT2" s="260"/>
+      <c r="FU2" s="260"/>
       <c r="FV2" s="128"/>
       <c r="FW2" s="128"/>
       <c r="FX2" s="128"/>
       <c r="FY2" s="111"/>
       <c r="FZ2" s="132"/>
-      <c r="GA2" s="250" t="s">
+      <c r="GA2" s="246" t="s">
         <v>95</v>
       </c>
-      <c r="GB2" s="250"/>
-      <c r="GC2" s="250"/>
-      <c r="GD2" s="250"/>
-      <c r="GE2" s="250"/>
-      <c r="GF2" s="250"/>
-      <c r="GG2" s="250"/>
+      <c r="GB2" s="246"/>
+      <c r="GC2" s="246"/>
+      <c r="GD2" s="246"/>
+      <c r="GE2" s="246"/>
+      <c r="GF2" s="246"/>
+      <c r="GG2" s="246"/>
       <c r="GH2" s="132"/>
       <c r="GI2" s="132"/>
       <c r="GJ2" s="132"/>
       <c r="GK2" s="111"/>
       <c r="GL2" s="142"/>
-      <c r="GM2" s="246" t="s">
+      <c r="GM2" s="257" t="s">
         <v>63</v>
       </c>
-      <c r="GN2" s="246"/>
-      <c r="GO2" s="246"/>
-      <c r="GP2" s="246"/>
-      <c r="GQ2" s="246"/>
-      <c r="GR2" s="246"/>
-      <c r="GS2" s="246"/>
+      <c r="GN2" s="257"/>
+      <c r="GO2" s="257"/>
+      <c r="GP2" s="257"/>
+      <c r="GQ2" s="257"/>
+      <c r="GR2" s="257"/>
+      <c r="GS2" s="257"/>
       <c r="GT2" s="142"/>
       <c r="GU2" s="142"/>
       <c r="GV2" s="142"/>
       <c r="GW2" s="111"/>
       <c r="GX2" s="143"/>
-      <c r="GY2" s="245" t="s">
+      <c r="GY2" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="GZ2" s="245"/>
-      <c r="HA2" s="245"/>
-      <c r="HB2" s="245"/>
-      <c r="HC2" s="245"/>
-      <c r="HD2" s="245"/>
-      <c r="HE2" s="245"/>
+      <c r="GZ2" s="256"/>
+      <c r="HA2" s="256"/>
+      <c r="HB2" s="256"/>
+      <c r="HC2" s="256"/>
+      <c r="HD2" s="256"/>
+      <c r="HE2" s="256"/>
       <c r="HF2" s="143"/>
       <c r="HG2" s="143"/>
       <c r="HH2" s="143"/>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="EX6" s="141">
         <f t="shared" si="62"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="EY6" s="141" t="str">
         <f t="shared" si="63"/>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="EX7" s="141">
         <f t="shared" si="62"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="EY7" s="141" t="str">
         <f t="shared" si="63"/>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="EX11" s="141">
         <f t="shared" si="62"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="EY11" s="141" t="str">
         <f t="shared" si="63"/>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="EX13" s="141">
         <f t="shared" si="62"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="EY13" s="141" t="str">
         <f t="shared" si="63"/>
@@ -20668,7 +20668,7 @@
       </c>
       <c r="EX18" s="141">
         <f t="shared" si="62"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="EY18" s="141" t="str">
         <f t="shared" si="63"/>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="EX19" s="141">
         <f t="shared" si="62"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="EY19" s="141" t="str">
         <f t="shared" si="63"/>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="EX22" s="141">
         <f t="shared" si="62"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EY22" s="141" t="str">
         <f t="shared" si="63"/>
@@ -24736,7 +24736,7 @@
       </c>
       <c r="EX24" s="141">
         <f t="shared" si="62"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="EY24" s="141" t="str">
         <f t="shared" si="63"/>
@@ -26130,7 +26130,7 @@
       </c>
       <c r="EX26" s="141">
         <f t="shared" si="62"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EY26" s="141" t="str">
         <f t="shared" si="63"/>
@@ -26844,7 +26844,7 @@
       </c>
       <c r="EX27" s="141">
         <f t="shared" si="62"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="EY27" s="141" t="str">
         <f t="shared" si="63"/>
@@ -27550,7 +27550,7 @@
       </c>
       <c r="EX28" s="141">
         <f t="shared" si="62"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="EY28" s="141" t="str">
         <f t="shared" si="63"/>
@@ -31016,23 +31016,23 @@
         <v>35</v>
       </c>
       <c r="EV33" s="215">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="EW33" s="49">
         <f t="shared" si="61"/>
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="EX33" s="141">
         <f t="shared" si="62"/>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="EY33" s="141" t="str">
         <f t="shared" si="63"/>
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="EZ33" s="141" t="str">
         <f t="shared" si="64"/>
-        <v>Credit</v>
+        <v>Excellent</v>
       </c>
       <c r="FA33" s="111">
         <v>30</v>
@@ -32434,7 +32434,7 @@
       </c>
       <c r="EX35" s="141">
         <f t="shared" si="62"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="EY35" s="141" t="str">
         <f t="shared" si="63"/>
@@ -33140,7 +33140,7 @@
       </c>
       <c r="EX36" s="141">
         <f t="shared" si="62"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="EY36" s="141" t="str">
         <f t="shared" si="63"/>
@@ -33846,7 +33846,7 @@
       </c>
       <c r="EX37" s="141">
         <f t="shared" si="62"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="EY37" s="141" t="str">
         <f t="shared" si="63"/>
@@ -34522,7 +34522,7 @@
       </c>
       <c r="EX38" s="141">
         <f t="shared" si="62"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="EY38" s="141" t="str">
         <f t="shared" si="63"/>
@@ -35940,7 +35940,7 @@
       </c>
       <c r="EX40" s="141">
         <f t="shared" si="62"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="EY40" s="141" t="str">
         <f t="shared" si="63"/>
@@ -37348,7 +37348,7 @@
       </c>
       <c r="EX42" s="141">
         <f t="shared" si="62"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="EY42" s="141" t="str">
         <f t="shared" si="63"/>
@@ -38012,7 +38012,7 @@
       </c>
       <c r="EX43" s="141">
         <f t="shared" si="62"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="EY43" s="141" t="str">
         <f t="shared" si="63"/>
@@ -43643,16 +43643,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="AA2:AG2"/>
-    <mergeCell ref="AY2:BE2"/>
-    <mergeCell ref="BK2:BQ2"/>
-    <mergeCell ref="P2:V2"/>
-    <mergeCell ref="BW2:CC2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CU2:DA2"/>
-    <mergeCell ref="DG2:DM2"/>
-    <mergeCell ref="DS2:DY2"/>
     <mergeCell ref="GY2:HE2"/>
     <mergeCell ref="GM2:GS2"/>
     <mergeCell ref="EE2:EK2"/>
@@ -43660,6 +43650,16 @@
     <mergeCell ref="FC2:FI2"/>
     <mergeCell ref="FO2:FU2"/>
     <mergeCell ref="GA2:GG2"/>
+    <mergeCell ref="BW2:CC2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CU2:DA2"/>
+    <mergeCell ref="DG2:DM2"/>
+    <mergeCell ref="DS2:DY2"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="AY2:BE2"/>
+    <mergeCell ref="BK2:BQ2"/>
+    <mergeCell ref="P2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43821,114 +43821,114 @@
       <c r="A10" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="299" t="e">
+      <c r="B10" s="261" t="e">
         <f>VLOOKUP(B14,Data!#REF!,2,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="299"/>
-      <c r="D10" s="299"/>
-      <c r="E10" s="299"/>
-      <c r="F10" s="299"/>
-      <c r="G10" s="299"/>
+      <c r="C10" s="261"/>
+      <c r="D10" s="261"/>
+      <c r="E10" s="261"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="261"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
-      <c r="K10" s="300" t="s">
+      <c r="K10" s="262" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="300"/>
-      <c r="M10" s="295" t="e">
+      <c r="L10" s="262"/>
+      <c r="M10" s="263" t="e">
         <f>VLOOKUP(B14,Data!#REF!,7,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="N10" s="296"/>
+      <c r="N10" s="264"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="293" t="e">
+      <c r="B11" s="265" t="e">
         <f>VLOOKUP(B14,Data!#REF!,4,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="293"/>
-      <c r="D11" s="293"/>
-      <c r="E11" s="293"/>
-      <c r="F11" s="293"/>
-      <c r="G11" s="293"/>
+      <c r="C11" s="265"/>
+      <c r="D11" s="265"/>
+      <c r="E11" s="265"/>
+      <c r="F11" s="265"/>
+      <c r="G11" s="265"/>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
-      <c r="K11" s="300" t="s">
+      <c r="K11" s="262" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="300"/>
-      <c r="M11" s="299" t="e">
+      <c r="L11" s="262"/>
+      <c r="M11" s="261" t="e">
         <f>VLOOKUP(B14,Data!#REF!,3,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="N11" s="301"/>
+      <c r="N11" s="266"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="299" t="e">
+      <c r="B12" s="261" t="e">
         <f>VLOOKUP(B14,Data!#REF!,5,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="299"/>
-      <c r="D12" s="299"/>
-      <c r="E12" s="299"/>
-      <c r="F12" s="299"/>
-      <c r="G12" s="299"/>
+      <c r="C12" s="261"/>
+      <c r="D12" s="261"/>
+      <c r="E12" s="261"/>
+      <c r="F12" s="261"/>
+      <c r="G12" s="261"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="300" t="s">
+      <c r="K12" s="262" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="300"/>
-      <c r="M12" s="299" t="e">
+      <c r="L12" s="262"/>
+      <c r="M12" s="261" t="e">
         <f>VLOOKUP(B14,Data!#REF!,8,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="N12" s="301"/>
+      <c r="N12" s="266"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="299" t="e">
+      <c r="B13" s="261" t="e">
         <f>VLOOKUP(B14,Data!#REF!,6,0)</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="299"/>
-      <c r="D13" s="299"/>
-      <c r="E13" s="299"/>
-      <c r="F13" s="299"/>
-      <c r="G13" s="299"/>
+      <c r="C13" s="261"/>
+      <c r="D13" s="261"/>
+      <c r="E13" s="261"/>
+      <c r="F13" s="261"/>
+      <c r="G13" s="261"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
-      <c r="K13" s="300" t="s">
+      <c r="K13" s="262" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="300"/>
-      <c r="M13" s="299" t="str">
+      <c r="L13" s="262"/>
+      <c r="M13" s="261" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="301"/>
+      <c r="N13" s="266"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="293">
+      <c r="B14" s="265">
         <v>30</v>
       </c>
-      <c r="C14" s="293"/>
+      <c r="C14" s="265"/>
       <c r="D14" s="64"/>
       <c r="E14" s="64"/>
       <c r="F14" s="64"/>
@@ -43936,10 +43936,10 @@
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
-      <c r="K14" s="294"/>
-      <c r="L14" s="294"/>
-      <c r="M14" s="295"/>
-      <c r="N14" s="296"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="267"/>
+      <c r="M14" s="263"/>
+      <c r="N14" s="264"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="63" t="s">
@@ -43957,10 +43957,10 @@
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
-      <c r="K15" s="297"/>
-      <c r="L15" s="297"/>
-      <c r="M15" s="294"/>
-      <c r="N15" s="298"/>
+      <c r="K15" s="268"/>
+      <c r="L15" s="268"/>
+      <c r="M15" s="267"/>
+      <c r="N15" s="269"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="63" t="s">
@@ -44000,111 +44000,111 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="264" t="s">
+      <c r="A18" s="293" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="266" t="s">
+      <c r="B18" s="295" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="295" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="266" t="s">
+      <c r="D18" s="295" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="266" t="s">
+      <c r="E18" s="295" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="268" t="s">
+      <c r="F18" s="297" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="266" t="s">
+      <c r="G18" s="295" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="266" t="s">
+      <c r="H18" s="295" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="268" t="s">
+      <c r="I18" s="297" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="270" t="s">
+      <c r="J18" s="299" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="285" t="s">
+      <c r="K18" s="270" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="286"/>
-      <c r="M18" s="287">
+      <c r="L18" s="271"/>
+      <c r="M18" s="272">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="288"/>
+      <c r="N18" s="273"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="265"/>
-      <c r="B19" s="267"/>
-      <c r="C19" s="267"/>
-      <c r="D19" s="267"/>
-      <c r="E19" s="267"/>
-      <c r="F19" s="269"/>
-      <c r="G19" s="267"/>
-      <c r="H19" s="267"/>
-      <c r="I19" s="269"/>
-      <c r="J19" s="271"/>
-      <c r="K19" s="289" t="s">
+      <c r="A19" s="294"/>
+      <c r="B19" s="296"/>
+      <c r="C19" s="296"/>
+      <c r="D19" s="296"/>
+      <c r="E19" s="296"/>
+      <c r="F19" s="298"/>
+      <c r="G19" s="296"/>
+      <c r="H19" s="296"/>
+      <c r="I19" s="298"/>
+      <c r="J19" s="300"/>
+      <c r="K19" s="274" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="290"/>
-      <c r="M19" s="277">
+      <c r="L19" s="275"/>
+      <c r="M19" s="276">
         <f>SUM(H23:H40)</f>
-        <v>1422</v>
-      </c>
-      <c r="N19" s="278"/>
+        <v>1480</v>
+      </c>
+      <c r="N19" s="277"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="265"/>
-      <c r="B20" s="267"/>
-      <c r="C20" s="267"/>
-      <c r="D20" s="267"/>
-      <c r="E20" s="267"/>
-      <c r="F20" s="269"/>
-      <c r="G20" s="267"/>
-      <c r="H20" s="267"/>
-      <c r="I20" s="269"/>
-      <c r="J20" s="271"/>
-      <c r="K20" s="289" t="s">
+      <c r="A20" s="294"/>
+      <c r="B20" s="296"/>
+      <c r="C20" s="296"/>
+      <c r="D20" s="296"/>
+      <c r="E20" s="296"/>
+      <c r="F20" s="298"/>
+      <c r="G20" s="296"/>
+      <c r="H20" s="296"/>
+      <c r="I20" s="298"/>
+      <c r="J20" s="300"/>
+      <c r="K20" s="274" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="290"/>
-      <c r="M20" s="291">
+      <c r="L20" s="275"/>
+      <c r="M20" s="278">
         <f>VLOOKUP(B14,Bsheet!A2:V51,21,0)</f>
-        <v>85.294117647058826</v>
-      </c>
-      <c r="N20" s="292"/>
+        <v>87</v>
+      </c>
+      <c r="N20" s="279"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="265"/>
-      <c r="B21" s="267"/>
-      <c r="C21" s="267"/>
-      <c r="D21" s="267"/>
-      <c r="E21" s="267"/>
-      <c r="F21" s="269"/>
-      <c r="G21" s="267"/>
-      <c r="H21" s="267"/>
-      <c r="I21" s="269"/>
-      <c r="J21" s="272"/>
-      <c r="K21" s="279" t="s">
+      <c r="A21" s="294"/>
+      <c r="B21" s="296"/>
+      <c r="C21" s="296"/>
+      <c r="D21" s="296"/>
+      <c r="E21" s="296"/>
+      <c r="F21" s="298"/>
+      <c r="G21" s="296"/>
+      <c r="H21" s="296"/>
+      <c r="I21" s="298"/>
+      <c r="J21" s="301"/>
+      <c r="K21" s="280" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="280"/>
-      <c r="M21" s="281">
+      <c r="L21" s="281"/>
+      <c r="M21" s="282">
         <f>VLOOKUP(B14,Bsheet!A2:V51,22,0)</f>
-        <v>2</v>
-      </c>
-      <c r="N21" s="282"/>
+        <v>1</v>
+      </c>
+      <c r="N21" s="283"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="265"/>
+      <c r="A22" s="294"/>
       <c r="B22" s="28" t="s">
         <v>58</v>
       </c>
@@ -44128,12 +44128,12 @@
       </c>
       <c r="I22" s="58"/>
       <c r="J22" s="59"/>
-      <c r="K22" s="283" t="s">
+      <c r="K22" s="284" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="283"/>
-      <c r="M22" s="283"/>
-      <c r="N22" s="284"/>
+      <c r="L22" s="284"/>
+      <c r="M22" s="284"/>
+      <c r="N22" s="285"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="29" t="s">
@@ -44175,13 +44175,13 @@
         <f>VLOOKUP(B14,Scoresheet!A4:K53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K23" s="276" t="str">
+      <c r="K23" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!A4:L53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L23" s="277"/>
-      <c r="M23" s="277"/>
-      <c r="N23" s="278"/>
+      <c r="L23" s="276"/>
+      <c r="M23" s="276"/>
+      <c r="N23" s="277"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="29" t="s">
@@ -44223,13 +44223,13 @@
         <f>VLOOKUP(B14,Scoresheet!M4:W53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K24" s="276" t="str">
+      <c r="K24" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!M4:X53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L24" s="277"/>
-      <c r="M24" s="277"/>
-      <c r="N24" s="278"/>
+      <c r="L24" s="276"/>
+      <c r="M24" s="276"/>
+      <c r="N24" s="277"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="29" t="s">
@@ -44271,13 +44271,13 @@
         <f>VLOOKUP(B14,Scoresheet!Y4:AI53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K25" s="276" t="str">
+      <c r="K25" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y4:AJ53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L25" s="277"/>
-      <c r="M25" s="277"/>
-      <c r="N25" s="278"/>
+      <c r="L25" s="276"/>
+      <c r="M25" s="276"/>
+      <c r="N25" s="277"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="29" t="s">
@@ -44319,13 +44319,13 @@
         <f>VLOOKUP(B14,Scoresheet!AK4:AU53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="276" t="str">
+      <c r="K26" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK4:AV53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L26" s="277"/>
-      <c r="M26" s="277"/>
-      <c r="N26" s="278"/>
+      <c r="L26" s="276"/>
+      <c r="M26" s="276"/>
+      <c r="N26" s="277"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="29" t="s">
@@ -44367,13 +44367,13 @@
         <f>VLOOKUP(B14,Scoresheet!AW4:BG53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K27" s="276" t="str">
+      <c r="K27" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW4:BH53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L27" s="277"/>
-      <c r="M27" s="277"/>
-      <c r="N27" s="278"/>
+      <c r="L27" s="276"/>
+      <c r="M27" s="276"/>
+      <c r="N27" s="277"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="29" t="s">
@@ -44415,13 +44415,13 @@
         <f>VLOOKUP(B14,Scoresheet!BI4:BU53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K28" s="276" t="str">
+      <c r="K28" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI4:BT53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L28" s="277"/>
-      <c r="M28" s="277"/>
-      <c r="N28" s="278"/>
+      <c r="L28" s="276"/>
+      <c r="M28" s="276"/>
+      <c r="N28" s="277"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="29" t="s">
@@ -44463,13 +44463,13 @@
         <f>VLOOKUP(B14,Scoresheet!BU4:CE53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K29" s="276" t="str">
+      <c r="K29" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU4:CF53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L29" s="277"/>
-      <c r="M29" s="277"/>
-      <c r="N29" s="278"/>
+      <c r="L29" s="276"/>
+      <c r="M29" s="276"/>
+      <c r="N29" s="277"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="29" t="s">
@@ -44511,13 +44511,13 @@
         <f>VLOOKUP(B14,Scoresheet!CG4:CQ53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K30" s="276" t="str">
+      <c r="K30" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG4:CR53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L30" s="277"/>
-      <c r="M30" s="277"/>
-      <c r="N30" s="278"/>
+      <c r="L30" s="276"/>
+      <c r="M30" s="276"/>
+      <c r="N30" s="277"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="29" t="s">
@@ -44559,13 +44559,13 @@
         <f>VLOOKUP(B14,Scoresheet!CS4:DC53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K31" s="276" t="str">
+      <c r="K31" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS4:DD53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L31" s="277"/>
-      <c r="M31" s="277"/>
-      <c r="N31" s="278"/>
+      <c r="L31" s="276"/>
+      <c r="M31" s="276"/>
+      <c r="N31" s="277"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="29" t="s">
@@ -44607,13 +44607,13 @@
         <f>VLOOKUP(B14,Scoresheet!DE4:DO53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K32" s="276" t="str">
+      <c r="K32" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE4:DP53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L32" s="277"/>
-      <c r="M32" s="277"/>
-      <c r="N32" s="278"/>
+      <c r="L32" s="276"/>
+      <c r="M32" s="276"/>
+      <c r="N32" s="277"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="29" t="s">
@@ -44655,13 +44655,13 @@
         <f>VLOOKUP(B14,Scoresheet!DQ4:EA53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K33" s="276" t="str">
+      <c r="K33" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ4:EB53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L33" s="277"/>
-      <c r="M33" s="277"/>
-      <c r="N33" s="278"/>
+      <c r="L33" s="276"/>
+      <c r="M33" s="276"/>
+      <c r="N33" s="277"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
@@ -44703,13 +44703,13 @@
         <f>VLOOKUP(B14,Scoresheet!EC4:EM53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K34" s="276" t="str">
+      <c r="K34" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC4:EN53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L34" s="277"/>
-      <c r="M34" s="277"/>
-      <c r="N34" s="278"/>
+      <c r="L34" s="276"/>
+      <c r="M34" s="276"/>
+      <c r="N34" s="277"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="29" t="s">
@@ -44737,27 +44737,27 @@
       </c>
       <c r="G35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:FA53,8,0)</f>
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,9,0)</f>
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I35" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,10,0)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J35" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K35" s="276" t="str">
+        <v>A</v>
+      </c>
+      <c r="K35" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO4:EZ53,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L35" s="277"/>
-      <c r="M35" s="277"/>
-      <c r="N35" s="278"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L35" s="276"/>
+      <c r="M35" s="276"/>
+      <c r="N35" s="277"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="29" t="s">
@@ -44799,13 +44799,13 @@
         <f>VLOOKUP(B14,Scoresheet!FA4:FK53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K36" s="276" t="str">
+      <c r="K36" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA4:FL53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L36" s="277"/>
-      <c r="M36" s="277"/>
-      <c r="N36" s="278"/>
+      <c r="L36" s="276"/>
+      <c r="M36" s="276"/>
+      <c r="N36" s="277"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="29" t="s">
@@ -44833,27 +44833,27 @@
       </c>
       <c r="G37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,8,0)</f>
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="H37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,9,0)</f>
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="I37" s="27">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,10,0)</f>
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J37" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO4:EY53,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K37" s="276" t="str">
+        <v>A</v>
+      </c>
+      <c r="K37" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM4:FX53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L37" s="277"/>
-      <c r="M37" s="277"/>
-      <c r="N37" s="278"/>
+      <c r="L37" s="276"/>
+      <c r="M37" s="276"/>
+      <c r="N37" s="277"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="29" t="s">
@@ -44895,13 +44895,13 @@
         <f>VLOOKUP(B14,Scoresheet!FY4:GI53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K38" s="276" t="str">
+      <c r="K38" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY4:GJ53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L38" s="277"/>
-      <c r="M38" s="277"/>
-      <c r="N38" s="278"/>
+      <c r="L38" s="276"/>
+      <c r="M38" s="276"/>
+      <c r="N38" s="277"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="29" t="s">
@@ -44943,13 +44943,13 @@
         <f>VLOOKUP(B14,Scoresheet!GK4:GV53,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K39" s="276" t="str">
+      <c r="K39" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK4:GW53,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L39" s="277"/>
-      <c r="M39" s="277"/>
-      <c r="N39" s="278"/>
+      <c r="L39" s="276"/>
+      <c r="M39" s="276"/>
+      <c r="N39" s="277"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="29" t="s">
@@ -44991,13 +44991,13 @@
         <f>VLOOKUP(B14,Scoresheet!GW4:HH53,11,0)</f>
         <v/>
       </c>
-      <c r="K40" s="276" t="str">
+      <c r="K40" s="286" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW4:HH53,12,0)</f>
         <v/>
       </c>
-      <c r="L40" s="277"/>
-      <c r="M40" s="277"/>
-      <c r="N40" s="278"/>
+      <c r="L40" s="276"/>
+      <c r="M40" s="276"/>
+      <c r="N40" s="277"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="22"/>
@@ -45021,20 +45021,20 @@
       </c>
       <c r="B42" s="35"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="274" t="s">
+      <c r="D42" s="287" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="274"/>
+      <c r="E42" s="287"/>
       <c r="F42" s="37"/>
       <c r="G42" s="38"/>
-      <c r="H42" s="275" t="s">
+      <c r="H42" s="288" t="s">
         <v>72</v>
       </c>
-      <c r="I42" s="275"/>
-      <c r="J42" s="275"/>
-      <c r="K42" s="275"/>
-      <c r="L42" s="275"/>
-      <c r="M42" s="275"/>
+      <c r="I42" s="288"/>
+      <c r="J42" s="288"/>
+      <c r="K42" s="288"/>
+      <c r="L42" s="288"/>
+      <c r="M42" s="288"/>
       <c r="N42" s="39"/>
       <c r="O42" s="17"/>
     </row>
@@ -45047,23 +45047,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="274" t="s">
+      <c r="D43" s="287" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="274"/>
+      <c r="E43" s="287"/>
       <c r="F43" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>3</v>
       </c>
       <c r="G43" s="38"/>
-      <c r="H43" s="275" t="s">
+      <c r="H43" s="288" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="275"/>
-      <c r="J43" s="275"/>
-      <c r="K43" s="275"/>
-      <c r="L43" s="275"/>
-      <c r="M43" s="275"/>
+      <c r="I43" s="288"/>
+      <c r="J43" s="288"/>
+      <c r="K43" s="288"/>
+      <c r="L43" s="288"/>
+      <c r="M43" s="288"/>
       <c r="N43" s="39"/>
       <c r="O43" s="17"/>
     </row>
@@ -45076,23 +45076,23 @@
         <v>3</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="274" t="s">
+      <c r="D44" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="274"/>
+      <c r="E44" s="287"/>
       <c r="F44" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>3</v>
       </c>
       <c r="G44" s="38"/>
-      <c r="H44" s="275" t="s">
+      <c r="H44" s="288" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="275"/>
-      <c r="J44" s="275"/>
-      <c r="K44" s="275"/>
-      <c r="L44" s="275"/>
-      <c r="M44" s="275"/>
+      <c r="I44" s="288"/>
+      <c r="J44" s="288"/>
+      <c r="K44" s="288"/>
+      <c r="L44" s="288"/>
+      <c r="M44" s="288"/>
       <c r="N44" s="39"/>
       <c r="O44" s="17"/>
     </row>
@@ -45105,23 +45105,23 @@
         <v>3</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="274" t="s">
+      <c r="D45" s="287" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="274"/>
+      <c r="E45" s="287"/>
       <c r="F45" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>5</v>
       </c>
       <c r="G45" s="38"/>
-      <c r="H45" s="275" t="s">
+      <c r="H45" s="288" t="s">
         <v>75</v>
       </c>
-      <c r="I45" s="275"/>
-      <c r="J45" s="275"/>
-      <c r="K45" s="275"/>
-      <c r="L45" s="275"/>
-      <c r="M45" s="275"/>
+      <c r="I45" s="288"/>
+      <c r="J45" s="288"/>
+      <c r="K45" s="288"/>
+      <c r="L45" s="288"/>
+      <c r="M45" s="288"/>
       <c r="N45" s="39"/>
       <c r="O45" s="17"/>
     </row>
@@ -45134,23 +45134,23 @@
         <v>2</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="274" t="s">
+      <c r="D46" s="287" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="274"/>
+      <c r="E46" s="287"/>
       <c r="F46" s="37">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>3</v>
       </c>
       <c r="G46" s="38"/>
-      <c r="H46" s="275" t="s">
+      <c r="H46" s="288" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="275"/>
-      <c r="J46" s="275"/>
-      <c r="K46" s="275"/>
-      <c r="L46" s="275"/>
-      <c r="M46" s="275"/>
+      <c r="I46" s="288"/>
+      <c r="J46" s="288"/>
+      <c r="K46" s="288"/>
+      <c r="L46" s="288"/>
+      <c r="M46" s="288"/>
       <c r="N46" s="39"/>
       <c r="O46" s="17"/>
     </row>
@@ -45163,23 +45163,23 @@
         <v>4</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="274" t="s">
+      <c r="D47" s="287" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="274"/>
+      <c r="E47" s="287"/>
       <c r="F47" s="37">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="38"/>
-      <c r="H47" s="275" t="s">
+      <c r="H47" s="288" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="275"/>
-      <c r="J47" s="275"/>
-      <c r="K47" s="275"/>
-      <c r="L47" s="275"/>
-      <c r="M47" s="275"/>
+      <c r="I47" s="288"/>
+      <c r="J47" s="288"/>
+      <c r="K47" s="288"/>
+      <c r="L47" s="288"/>
+      <c r="M47" s="288"/>
       <c r="N47" s="39"/>
       <c r="O47" s="17"/>
     </row>
@@ -45284,11 +45284,11 @@
       <c r="O52" s="17"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="261" t="s">
+      <c r="A53" s="289" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="262"/>
-      <c r="C53" s="262"/>
+      <c r="B53" s="290"/>
+      <c r="C53" s="290"/>
       <c r="D53" s="17" t="s">
         <v>79</v>
       </c>
@@ -45306,16 +45306,16 @@
       <c r="M53" s="17"/>
       <c r="N53" s="15"/>
       <c r="O53" s="17"/>
-      <c r="R53" s="263"/>
-      <c r="S53" s="263"/>
-      <c r="T53" s="263"/>
+      <c r="R53" s="292"/>
+      <c r="S53" s="292"/>
+      <c r="T53" s="292"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="261" t="s">
+      <c r="A54" s="289" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="262"/>
-      <c r="C54" s="262"/>
+      <c r="B54" s="290"/>
+      <c r="C54" s="290"/>
       <c r="D54" s="17" t="s">
         <v>79</v>
       </c>
@@ -45330,43 +45330,43 @@
       <c r="M54" s="17"/>
       <c r="N54" s="15"/>
       <c r="O54" s="17"/>
-      <c r="R54" s="263"/>
-      <c r="S54" s="263"/>
-      <c r="T54" s="263"/>
+      <c r="R54" s="292"/>
+      <c r="S54" s="292"/>
+      <c r="T54" s="292"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="261" t="s">
+      <c r="A55" s="289" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="262"/>
-      <c r="C55" s="262"/>
+      <c r="B55" s="290"/>
+      <c r="C55" s="290"/>
       <c r="D55" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="273" t="str">
+      <c r="E55" s="291" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="273"/>
-      <c r="G55" s="273"/>
-      <c r="H55" s="273"/>
-      <c r="I55" s="273"/>
-      <c r="J55" s="273"/>
+      <c r="F55" s="291"/>
+      <c r="G55" s="291"/>
+      <c r="H55" s="291"/>
+      <c r="I55" s="291"/>
+      <c r="J55" s="291"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" s="15"/>
       <c r="O55" s="17"/>
-      <c r="R55" s="263"/>
-      <c r="S55" s="263"/>
-      <c r="T55" s="263"/>
+      <c r="R55" s="292"/>
+      <c r="S55" s="292"/>
+      <c r="T55" s="292"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="261" t="s">
+      <c r="A56" s="289" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="262"/>
-      <c r="C56" s="262"/>
+      <c r="B56" s="290"/>
+      <c r="C56" s="290"/>
       <c r="D56" s="17" t="s">
         <v>79</v>
       </c>
@@ -45384,9 +45384,9 @@
       <c r="M56" s="17"/>
       <c r="N56" s="15"/>
       <c r="O56" s="17"/>
-      <c r="R56" s="263"/>
-      <c r="S56" s="263"/>
-      <c r="T56" s="263"/>
+      <c r="R56" s="292"/>
+      <c r="S56" s="292"/>
+      <c r="T56" s="292"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="24"/>
@@ -45423,65 +45423,6 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -45498,6 +45439,65 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -48860,7 +48860,7 @@
       </c>
       <c r="V20" s="97">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -49807,7 +49807,7 @@
       </c>
       <c r="N31" s="3">
         <f>Scoresheet!EW33</f>
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="O31" s="3">
         <f>Scoresheet!FI33</f>
@@ -49831,15 +49831,15 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="0"/>
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="U31" s="57">
         <f t="shared" si="1"/>
-        <v>85.294117647058826</v>
+        <v>87</v>
       </c>
       <c r="V31" s="97">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:22">
